--- a/docs/testcases/manzil-mobile-testcases.xlsx
+++ b/docs/testcases/manzil-mobile-testcases.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Приложение склада" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Приложение перевозчика" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Мобайл — Склад" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Мобайл — Перевозчик" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,11 +32,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,28 +87,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -492,14 +472,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -520,75 +499,59 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Покрытие</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>Кейсов</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение склада (SHIPPER_WAREHOUSE)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Приложение склада</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Вход · вкладки статусов · создание заявки (тип ТС, водители, маршрут, адреса) · детали · связь · отправка груза · профиль</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Мобайл — Warehouse-app</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Мобайл — Склад</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Логин · создание заявки · адрес (cityId) · публикация · lifecycle · связь · goods-sent</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика (TRANSPORT_ADMIN)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Вход (wrong-app) · лента заказов · офферы · водители · назначение (busy/blacklist/plate) · старт работы</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Мобайл — Carrier-app</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Мобайл — Перевозчик</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Логин · лента · предложение · водители · назначение · старт заявки</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="7" t="n">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
         <v>119</v>
       </c>
     </row>
@@ -606,8 +569,8 @@
   <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
@@ -615,7 +578,7 @@
     <col width="56" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -671,32 +634,32 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Happy path: вход по телефону (9 цифр) и паролю без OTP</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Приложение склада установлено, смотрит на staging. Есть рабочая учётка SHIPPER_WAREHOUSE (+998900000004 / &lt;staging-password&gt;)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>1. Открыть приложение
 2. Дождаться экрана входа с логотипом MANZIL и подписью «Hisobingizga kiring»
@@ -706,50 +669,50 @@
 6. Нажать «Kirish»</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Вход успешен. Открывается главный экран «Buyurtmalar» со списком заявок и зелёной FAB «Ariza yaratish». Нижняя навигация Buyurtmalar/Profil видна</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Kirish» неактивна при пустых полях</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>1. Не заполнять поля
 2. Оценить состояние кнопки «Kirish»
@@ -757,199 +720,199 @@
 4. Заполнить только пароль (телефон пуст) — оценить кнопку</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Пока оба поля не заполнены, кнопка «Kirish» бледная/неактивная и не реагирует на тап. Синей (активной) становится только когда заполнены и телефон, и пароль</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>mobile|validation|negative</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Неверный пароль → ошибка «Noto'g'ri login yoki parol» (401)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа. Известен валидный телефон</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>1. Ввести валидный телефон 900000004
 2. Ввести заведомо неверный пароль
 3. Нажать «Kirish»</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Вход отклонён (сервер 401 error.invalid-credentials). Показан узбекский текст «Noto'g'ri login yoki parol». Пользователь остаётся на экране входа, поля сохранены</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|validation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Чужая роль/среда → 403 wrong-app, остаётся на входе</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа. Есть учётка НЕ SHIPPER_WAREHOUSE (напр. SHIPPER_MANAGER +998900000003)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>1. Ввести телефон 900000003 и его корректный пароль
 2. Нажать «Kirish»</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Вход отклонён гейтом clientType=WAREHOUSE_APP (сервер 403 wrong-app). Пользователь остаётся на экране входа, в приложение не пускает. Текст ошибки — (проверить на устройстве: узб. сообщение о неверном приложении)</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Вход отклонён гейтом clientType=WAREHOUSE_APP (сервер 403 wrong-app): пользователь остаётся на экране входа, внутрь не пускает. Проверено 2026-07-17: отказ работает; текст ошибки сейчас английский generic «Access denied» вместо локализованного узбекского сообщения (→ BUG-028).</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>mobile|rbac|negative</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Показ/скрытие пароля иконкой-глаз</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>1. Ввести пароль в поле «Parol» (по умолчанию точечная маскировка)
 2. Тапнуть иконку-глаз
 3. Тапнуть иконку-глаз повторно</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>По умолчанию пароль скрыт точками. После тапа по глазу пароль отображается открытым текстом. Повторный тап снова маскирует</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Поле телефона: фиксированный +998, ввод 9 национальных цифр с маской</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>1. Оценить префикс поля телефона
 2. Начать вводить цифры номера
@@ -957,688 +920,688 @@
 4. Попробовать ввести буквы/символы</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Слева зафиксированы флаг и «+998» (стрелка-dropdown рядом). Ввод только национальной части — 9 цифр, накладывается маска «99 474 60 06». Свыше 9 цифр не принимается; буквы не вводятся (проверить на устройстве)</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Слева зафиксированы флаг и «+998» (стрелка-dropdown рядом). Ввод только национальной части — 9 цифр с маской «99 474 60 06». Свыше 9 цифр не принимается; буквы не вводятся. Проверено вручную 2026-07-17: лимит 9 цифр и запрет букв работают.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-008</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Системный диалог разрешения на уведомления при первом запуске</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Свежая установка приложения (clearState), Android 13+</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>1. Впервые запустить приложение
 2. Дождаться системного диалога Android «Allow notifications?»
 3. Проверить оба варианта (Allow / Don't allow) на отдельных прогонах</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Показан системный диалог уведомлений. Выбор «Allow» или «Don't allow» не блокирует вход — экран входа доступен после закрытия диалога</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-010</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Лимит попыток входа: 5 неудач/телефон → 429</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа. Тест проводить осторожно (лимитер: 5 неудач/телефон, 30/IP, окно 10 мин)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>1. Ввести валидный телефон и неверный пароль
 2. Нажать «Kirish»
 3. Повторить неверный вход 5 раз подряд для одного телефона</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>После исчерпания лимита сервер отвечает 429 (too many requests). Приложение показывает сообщение об ограничении/повторе позже (проверить на устройстве текст). Дальнейшие попытки блокируются до конца окна 10 мин</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>После 5 неудачных попыток на телефон сервер отвечает 429; приложение показывает сообщение об ограничении. Проверено 2026-07-17: после 5 попыток появляется «Too many requests» (429 работает). Текст английский, не локализован (→ BUG-028).</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|session</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-013</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Вкладки статусов со счётчиками отображаются</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход, открыт список заявок</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть верхнюю ленту вкладок статусов
 2. Сверить набор вкладок и счётчики</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Видны вкладки со счётчиками: «E'lon qilindi» [PUBLISHED], «Olingan» [взятые], «Ishda» [IN_WORK], «Yo'lda» [IN_TRANSIT], «Tugallangan» [COMPLETED]. Счётчик у вкладки соответствует числу заявок в статусе (сверить с /orders/summary)</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|state</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-014</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Горизонтальная прокрутка ленты вкладок к «Tugallangan»</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. Много заявок → вкладки переполняют строку</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>1. Заметить, что крайняя вкладка «Tugallangan» уходит за правый край
 2. Свайпнуть ленту вкладок влево
 3. Тапнуть вкладку «Tugallangan»</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Лента вкладок горизонтально прокручивается, «Tugallangan» становится видимой и открывается. Крайние левые вкладки не должны пропадать без прокрутки</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|state</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-015</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Переключение между вкладками фильтрует список по статусу</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. Есть заявки в разных статусах</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть вкладку «E'lon qilindi» — оценить список
 2. Тапнуть «Ishda» — оценить список
 3. Тапнуть «Yo'lda» — оценить список</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Список перерисовывается под выбранный статус. На вкладке «E'lon qilindi» показываются PUBLISHED (включая свёрнутые QUOTED). CANCELLED/SUPERSEDED нигде не отображаются</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|state|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-016</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Содержимое карточки заявки: номер, дата, маршрут, тип ТС</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. На вкладке есть заявки</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>1. Рассмотреть карточку заявки
 2. Сверить отображаемые поля</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Карточка показывает: номер вида «NAMA-00010» (staging-префикс NAMA), дату загрузки, блок маршрута — зелёная точка = отправление (город/склад), стрелка ---&gt;, красная метка = назначение, чип типа ТС «Bortli 13.7». Маршруты реальные CN↔CIS (Urumqi, Yiwu, Nukus, Almata, Beijing)</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-017</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Дефект: пустой тип ТС отображается как «—»</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Пустой тип ТС отображается как «—»</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. Есть заявка без типа ТС (напр. NAMA-00009 Nukus→Almata)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>1. Найти карточку заявки без типа транспорта
 2. Осмотреть чип типа ТС</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>⚠ ДЕФЕКТ/наблюдение: у части заявок чип типа ТС пуст и показывает «—». Уточнить, допустима ли публикация без типа ТС (по API vehicleTypeId обязателен при создании) — возможно легаси-данные. Отобразить осмысленный плейсхолдер вместо «—»</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>У части заявок чип типа ТС пуст и показывает «—» (вероятно легаси-данные; по API vehicleTypeId обязателен при создании). Ожидается осмысленный плейсхолдер вместо «—».</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|state</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-018</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Пустое состояние вкладки без заявок</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. Есть вкладка со счётчиком 0 (напр. «Yo'lda (0)»)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>1. Открыть вкладку без заявок</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Список пуст, показано пустое состояние (иллюстрация/текст «нет заявок»). Приложение не падает и не показывает бесконечный лоадер. (Проверить на устройстве точный текст пустого состояния)</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Список пуст, показано пустое состояние с текстом (напр. «Пока нет заказов»). Приложение не падает, нет бесконечного лоадера. Проверено 2026-07-17: пустое состояние показано, текст локализован.</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|state</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-019</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Открытие деталей заявки по тапу на карточку</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. На вкладке есть заявка</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть по карточке заявки</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Открывается экран деталей выбранной заявки (секции, статусная лента). Данные соответствуют карточке (маршрут, дата, тип ТС)</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-021</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Выбор типа транспорта (Transport turini tanlang)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Открытие шага выбора транспорта по FAB, «Avtomobil» активен</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход, открыт список заявок</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>1. Нажать зелёную FAB «+» (Ariza yaratish)
 2. Дождаться bottom sheet «Transport turini tanlang»
 3. Оценить карточки «Temir yo'l» и «Avtomobil»</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Открывается bottom sheet с заголовком «Transport turini tanlang». Карточка «Avtomobil» активна (выделена зелёным). Карточка «Temir yo'l» серая/недоступна</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-022</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Выбор типа транспорта (Transport turini tanlang)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>«Temir yo'l» недоступен для выбора</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Открыт bottom sheet «Transport turini tanlang»</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть по серой карточке «Temir yo'l»</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Выбор не срабатывает, переход к форме не происходит. Ж/д тип недоступен (в разработке). Форма создания открывается только для «Avtomobil»</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-023</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Выбор типа транспорта (Transport turini tanlang)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Выбор «Avtomobil» открывает форму «Yangi ariza yaratish»</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Открыт bottom sheet «Transport turini tanlang»</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть «Avtomobil»</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Открывается форма «Yangi ariza yaratish» с полями: Yuklash sanasi, Transport (чипы), Haydovchilar soni, Yo'nalish, Izohlar. Внизу «Orqaga» / «Ko'rib chiqish». cargoType=AUTO</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-024</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Дата загрузки по умолчанию = сегодня</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Открыта форма «Yangi ariza yaratish»</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть поле «Yuklash sanasi *»
 2. Сверить значение по умолчанию</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Поле «Yuklash sanasi» с иконкой-календарём предзаполнено сегодняшней датой (напр. «10 Iyul · Ju»). Дата в зоне Asia/Tashkent</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-025</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Выбор даты загрузки через календарь (будущая дата)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Открыта форма «Yangi ariza yaratish»</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть поле «Yuklash sanasi»
 2. Открыть календарь
@@ -1646,100 +1609,100 @@
 4. Подтвердить</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Календарь открывается, выбранная будущая дата подставляется в поле. Даты в прошлом либо недоступны, либо приведут к серверной ошибке error.order.load-not-after-publish при публикации (проверить поведение UI)</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Календарь открывается, выбранная будущая дата подставляется в поле. Даты в прошлом недоступны в календаре либо при публикации отклоняются сервером (error.order.load-not-after-publish).</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|validation</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Выбор типа ТС из чипов Transport (одиночный выбор)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Открыта форма «Yangi ariza yaratish»</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть чипы «Transport *»
 2. Тапнуть «Bortli 13.7»
 3. Тапнуть другой чип «Refrijerator 12.5»</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Доступны чипы: Bortli 13.7, Bortli 16, Bortli 17.5, Refrijerator 12.5, Baland bortli 13, Tentli 9.6. Выбор одиночный — при выборе нового чипа предыдущий снимается. Выбранный чип визуально выделен</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|validation</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-027</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Выбор количества водителей: 1 vs 2 haydovchi</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Открыта форма «Yangi ariza yaratish»</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть «Haydovchilar soni *»
 2. Проверить значение по умолчанию
@@ -1747,296 +1710,296 @@
 4. Вернуть «1 haydovchi»</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>По умолчанию выбрано «1 haydovchi». Переключение на «2 haydovchi» работает (одиночный выбор). Значения ограничены 1 и 2 (по API driversCount @Min(1)@Max(2))</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|boundary</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-028</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Предзаполнение маршрута сохранёнными складами</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Учётка с сохранёнными складами (напр. Nukus→Almata). Открыта форма</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть секцию «Yo'nalish *»
 2. Сверить предзаполненные точки</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Секция «Yo'nalish» предзаполнена дефолтными складами аккаунта: «откуда» (зелёная точка, город+склад) → «куда» (красная метка). Значения берутся из GET /locations/from и /locations/to (isDefault)</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-029</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Валидация: обязательные поля не заполнены → «Ko'rib chiqish» не пускает дальше</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Свежая учётка без сохранённых складов ИЛИ снят тип ТС. Открыта форма</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>1. Не выбирать тип ТС и/или не задать маршрут
 2. Нажать «Ko'rib chiqish»</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Переход к просмотру блокируется. Показаны подсветки/сообщения у незаполненных обязательных полей (Yuklash sanasi, Transport, Haydovchilar soni, Yo'nalish). Кнопка «Ko'rib chiqish» неактивна либо валидация выводит ошибку (проверить на устройстве)</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Кнопка «Ko'rib chiqish» неактивна, пока не заполнены обязательные поля — дальше не пускает, пустую заявку создать нельзя. Проверено 2026-07-17: кнопка неактивна до заполнения.</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|validation</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-030</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Поле комментариев Izohlar необязательное</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Открыта форма «Yangi ariza yaratish»</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть поле «Izohlar» с плейсхолдером «Maxsus talablar...»
 2. Оставить пустым и пройти дальше
 3. На другом прогоне ввести текст комментария</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Поле «Izohlar» необязательное (без звёздочки): пустое не мешает публикации. Введённый текст сохраняется и уходит в notes (лимит 2000 символов на сервере)</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-031</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Orqaga» возвращает без сохранения черновика</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Открыта форма «Yangi ariza yaratish», часть полей заполнена</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>1. Заполнить тип ТС и число водителей
 2. Нажать «Orqaga» (или стрелку назад в шапке)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Возврат на предыдущий экран/список. Заявка не создаётся (POST не отправляется). Поведение по несохранённым данным — (проверить на устройстве: предупреждение о потере или молчаливый выход)</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>«Orqaga» возвращает без сохранения: повторный вход в создание заявки открывает чистую форму, черновик не хранится. Проверено 2026-07-17: форма чистая.</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-032</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Открытие списка адресов и добавление нового своего адреса</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Свежая учётка без сохранённых складов. В форме создания показаны плейсхолдеры «Yuklash manzili»/«Yetkazib berish manzili»</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть «Yuklash manzili»
 2. В шите тапнуть «O'z manzilingizni qo'shish»</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Открывается форма добавления адреса: выбор страны (Xitoy/Qirg'iziston), поиск города «Shaharni qidirish» и поле точного адреса «Ko'cha, uy, xonadon»</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-033</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Поиск города и сохранение адреса загрузки (Xitoy)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Открыта форма добавления адреса</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть страну «Xitoy»
 2. Тапнуть «Shaharni qidirish», ввести «Beijing»
@@ -2046,50 +2009,50 @@
 6. Нажать «Manzilni saqlash»</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Город найден поиском и выбран (передаётся реальный cityId). Адрес сохранён (POST /warehouse/locations → 201) и подставлен в точку «откуда» маршрута. Плейсхолдер «Yuklash manzili» заменён сохранённым адресом</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-034</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Добавление адреса доставки (Yetkazib berish manzili)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Адрес загрузки уже добавлен. Плейсхолдер «Yetkazib berish manzili» показан</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть «Yetkazib berish manzili»
 2. «O'z manzilingizni qo'shish» → «Xitoy»
@@ -2098,1102 +2061,1102 @@
 5. Нажать «Manzilni saqlash»</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Адрес доставки сохранён и подставлен в точку «куда» (красная метка). Маршрут «Yo'nalish» полностью заполнен (from→to), можно переходить к «Ko'rib chiqish»</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-035</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Валидация: сохранение без точного адреса</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Открыта форма добавления адреса, выбран город</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>1. Выбрать страну и город
 2. Оставить «Ko'cha, uy, xonadon» пустым
 3. Нажать «Manzilni saqlash»</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Сохранение блокируется / выводится ошибка обязательности адреса (по API address-required при ad-hoc, name @NotBlank при своём складе). Пустой адрес не принимается (проверить точный текст на устройстве)</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Сохранение блокируется при пустом точном адресе: кнопка «Manzilni saqlash» неактивна. Проверено 2026-07-17: кнопка неактивна без адреса.</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|validation</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-036</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Выбор страны Qirg'iziston как альтернативы Xitoy</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Открыта форма добавления адреса</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>1. Открыть выбор страны
 2. Выбрать «Qirg'iziston» (если доступна)
 3. Найти город и сохранить адрес</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Доступны страны Xitoy (CN) и Qirg'iziston (KG) (по API divisionCountry ограничен CN|KG). Для KG поиск города и сохранение работают аналогично. (Проверить наличие KG на устройстве)</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Доступны страны Xitoy (CN) и Qirg'iziston (KG). Для KG поиск города и сохранение адреса работают аналогично Китаю. Проверено 2026-07-17: работает как для Китая.</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|validation</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-037</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Существующий сохранённый адрес выбирается из списка без повторного ввода</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Учётка с уже сохранёнными складами</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>1. В форме создания тапнуть точку маршрута (стрелку-редактирование)
 2. Выбрать сохранённый адрес из списка (без «O'z manzilingizni qo'shish»)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Ранее сохранённые склады показаны списком, выбор подставляется в маршрут мгновенно (fromWarehouseId/toWarehouseId), без формы добавления. Блок добавления пропускается</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-038</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Просмотр заявки (Ko'rib chiqish)</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Экран просмотра перед публикацией отображает введённые данные</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Форма заполнена (тип ТС, водители, маршрут from→to)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>1. Нажать «Ko'rib chiqish»</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Открывается экран просмотра с итоговыми данными заявки: дата загрузки, тип ТС, число водителей, маршрут, комментарии. Присутствует кнопка «E'lon qilish» (публикация)</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-039</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Просмотр заявки (Ko'rib chiqish)</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Публикация заявки: «E'lon qilish» → появление на вкладке «E'lon qilindi»</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Открыт экран просмотра корректно заполненной заявки. loadDate=сегодня, без scheduledPublishDate</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>1. Нажать «E'lon qilish»
 2. Дождаться возврата к списку
 3. Открыть вкладку «E'lon qilindi»</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Заявка создаётся и публикуется немедленно (POST /orders → 201, status=PUBLISHED, currency=CNY по умолчанию, присвоен NAMA-xxxxx). Заявка видна на вкладке «E'lon qilindi», счётчик увеличился</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-040</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Просмотр заявки (Ko'rib chiqish)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Защита от двойной публикации при повторных тапах «E'lon qilish»</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Защита от двойной публикации при повторных тапах «E'lon qilish»</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Открыт экран просмотра заявки</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>1. Быстро дважды тапнуть «E'lon qilish»
 2. Проверить список на вкладке «E'lon qilindi»</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Создаётся ровно одна заявка. Кнопка должна блокироваться/показывать лоадер после первого тапа. ⚠ Проверить отсутствие дубля (два POST /orders) при быстром двойном тапе</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Создаётся ровно одна заявка. Кнопка должна блокироваться/показывать лоадер после первого тапа (без дубля POST /orders при быстром двойном тапе).</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|network</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-042</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Секции деталей и статусная лента</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. Открыта заявка тапом с любой вкладки</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>1. Открыть детали заявки
 2. Осмотреть секции и статус</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Показаны секции заявки (маршрут, дата, тип ТС, число водителей, комментарии) и статусная лента, соответствующая вкладке. Внутренний «ID» может отличаться от отображаемого номера NAMA-xxxxx</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-043</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Информация о водителе и госномере в IN_WORK</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Есть заявка «Ishda» (IN_WORK) с прикреплённым водителем</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>1. Открыть вкладку «Ishda»
 2. Открыть заявку с водителем
 3. Найти секцию «Haydovchi ma'lumotlari»</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Показана секция «Haydovchi ma'lumotlari» с ФИО водителя, строка «Davlat raqami» (госномер). Данные из GET /orders/{id} (drivers: name/phone/cardId/plate)</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-044</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Связь с водителем: диалог «Haydovchi bilan aloqa» доступен только в IN_WORK</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Заявка «Ishda» (IN_WORK)</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>1. Открыть заявку IN_WORK
 2. Тапнуть строку «Haydovchi bilan aloqa»
 3. Оценить диалог «Haydovchi bilan bog'landingizmi?»</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Открывается диалог с вариантами: «Tasdiqlandi» (CONFIRMED), «Rad etildi» (DECLINED), «Aloqasiz» (UNAVAILABLE), «Bog'lanish» (PENDING). Доступно только в IN_WORK (по API communication только IN_WORK, иначе 409 not-communicable)</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-045</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Установка статуса связи «Tasdiqlandi» (CONFIRMED)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Открыта заявка IN_WORK, открыт диалог связи</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>1. Выбрать «Tasdiqlandi»
 2. Вернуться к деталям</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Статус связи меняется на «Tasdiqlandi» (POST /communication → 204). Отображение в деталях обновляется. Это разблокирует отправку груза</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-046</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Смена статуса связи на другие значения (Rad etildi/Aloqasiz)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Открыта заявка IN_WORK</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>1. Открыть «Haydovchi bilan aloqa»
 2. Выбрать «Rad etildi»
 3. Повторно открыть и выбрать «Aloqasiz»</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Каждая смена принимается (204), статус связи перезаписывается (ортогональный суб-статус, заявка остаётся IN_WORK). UI отражает актуальный выбор</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-047</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Отправка груза «Yuk jo'natildi» → «Yo'lda» (IN_TRANSIT)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Заявка IN_WORK со статусом связи «Tasdiqlandi» (CONFIRMED)</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>1. Нажать «Yuk jo'natildi»
 2. В диалоге «Yuk jo'natilganini tasdiqlaysizmi?» подтвердить (тап «Yuk jo'natildi»)
 3. Проверить статус/вкладку</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Груз отправлен (POST /goods-sent → 200), заявка переходит в «Yo'lda» (IN_TRANSIT). Появляется на вкладке «Yo'lda»</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-048</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Запрет отправки груза без подтверждения связи (не CONFIRMED)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Заявка IN_WORK, статус связи НЕ «Tasdiqlandi» (напр. PENDING/DECLINED)</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>1. Открыть заявку IN_WORK без CONFIRMED
 2. Попытаться нажать «Yuk jo'natildi»</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Yuk jo'natildi» неактивна ИЛИ отправка отклоняется (сервер 409 error.order.not-ready-for-transit). Груз нельзя отправить, пока связь не «Tasdiqlandi»</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-049</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Дефект: не-идемпотентная повторная отправка груза</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Повторная отправка груза (идемпотентность)</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Заявка уже переведена в «Yo'lda» (IN_TRANSIT) после первого «Yuk jo'natildi»</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>1. Быстро дважды подтвердить в диалоге «Yuk jo'natildi»
 2. Либо открыть уже IN_TRANSIT заявку и снова попытаться отправить груз</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>⚠ ДЕФЕКТ-риск: goods-sent не идемпотентен (повтор на IN_TRANSIT → 409 error.order.not-ready-for-transit). При двойном тапе UI не должен показывать ошибку/дубль — кнопку блокировать после первого подтверждения. Проверить обработку 409 на экране</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>goods-sent не идемпотентен (повтор на IN_TRANSIT → 409 error.order.not-ready-for-transit). UI должен блокировать кнопку после первого подтверждения и корректно обрабатывать 409, без ошибки/дубля.</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|network|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-050</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Связь и отправка груза недоступны вне IN_WORK</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Заявка в статусе PUBLISHED («E'lon qilindi») или IN_TRANSIT («Yo'lda»)</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>1. Открыть заявку не в IN_WORK
 2. Поискать строку «Haydovchi bilan aloqa» и кнопку «Yuk jo'natildi»</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Действия связи и отправки груза не показываются/недоступны вне IN_WORK. На PUBLISHED communication → 409 not-communicable, goods-sent → 409 not-ready. UI не должен предлагать эти действия</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>mobile|negative|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-052</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Отображение ФИО и телефона профиля</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть «Profil» в нижней навигации
 2. Осмотреть шапку профиля</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>Показан аватар с инициалами, ФИО (напр. «Бегимбаев Наврузбек Мамбетали») и телефон «+998900000004». Данные соответствуют вошедшему пользователю</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-053</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Пункт «Bildirishnomalar» (уведомления)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Открыт экран профиля</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть карточку «Bildirishnomalar»</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Открывается экран/настройки уведомлений. Содержимое — (проверить на устройстве: список уведомлений или тумблеры)</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Пункт «Bildirishnomalar»/«Уведомления» в профиле открывает экран уведомлений со списком (или пустым состоянием). Приложение не падает. Проверено 2026-07-17: открывается список уведомлений.</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-055</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Выход «Chiqish» возвращает на экран входа</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Открыт экран профиля</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть «Chiqish»
 2. Подтвердить выход, если запрошено</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>Сессия завершается, токен сбрасывается. Приложение возвращается на экран входа «Hisobingizga kiring». Повторный вход требует телефон+пароль. Список заявок недоступен без входа</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>mobile|session|positive</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-059</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Протухший/невалидный токен → релогин</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. Токен инвалидирован (истёк или отозван на бэке)</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>1. Оставить приложение и дождаться истечения токена (или отозвать сессию)
 2. Выполнить действие, требующее авторизации (открыть заявку/обновить список)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Сервер отвечает 401. Приложение выкидывает на экран входа для релогина (не показывает бесконечную ошибку). После входа доступ восстанавливается</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>mobile|session|negative</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-060</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Фон/возврат приложения сохраняет сессию</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход, открыт список заявок</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>1. Свернуть приложение (Home)
 2. Открыть другое приложение
 3. Вернуться к приложению склада</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Приложение восстанавливается на том же экране, сессия жива (без повторного входа при валидном токене). Список актуален или перезагружается</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>mobile|session|positive</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-062</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Повторные тапы по FAB не открывают несколько форм</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход, открыт список заявок</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>1. Быстро несколько раз тапнуть FAB «Ariza yaratish»</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Открывается ровно один bottom sheet «Transport turini tanlang». Множественные экраны/дубли не создаются</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>MOB-WH-065</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Пустой список после выхода/входа другой учёткой (изоляция компаний)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Есть две учётки SHIPPER_WAREHOUSE разных компаний</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>1. Войти учёткой компании A, запомнить заявки
 2. Выйти («Chiqish»)
 3. Войти учёткой компании B</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>Показаны только заявки компании B. Заявки компании A не видны (tenancy: список scoped по shipperCompanyId). Данные предыдущей сессии не утекают</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>mobile|session|rbac</t>
         </is>
@@ -3213,8 +3176,8 @@
   <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
@@ -3222,7 +3185,7 @@
     <col width="56" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3278,32 +3241,32 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Happy path: вход TRANSPORT_ADMIN по телефону и паролю (200)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Установлено приложение перевозчика uz.logos.manzil.driver (clientType=TRANSPORT_COMPANY_APP), смотрит на staging-manzil.greatmall.uz. Есть учётка роли TRANSPORT_ADMIN (например +998900000002 / &lt;staging-password&gt;). Экран входа наблюдался вживую.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>1. Запустить приложение, дождаться экрана «Yana xush kelibsiz» (логотип «M Manzil», подзаголовок про грузы и маршруты).
 2. В поле «Telefon raqam» (слева флаг и «+998 ⌄», плейсхолдер «00 000 00 00») ввести 9 цифр номера.
@@ -3312,250 +3275,250 @@
 5. Нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Вход выполнен (сервер 200 /auth/login + 200 /me). Открывается главный экран «Mavjud yuklar». Баннер ошибки не появляется.</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Неверный пароль → 401 invalid-credentials</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Есть валидный телефон TRANSPORT_ADMIN. Экран входа наблюдался вживую.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>1. Ввести корректный телефон.
 2. Ввести заведомо неверный пароль.
 3. Нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Вход отклонён (сервер 401, code=error.invalid-credentials). Показывается сообщение об ошибке логина/пароля; пользователь остаётся на экране входа, поля сохранены.</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Чужая роль SHIPPER_MANAGER в carrier-app → 403 wrong-app (ФАКТ, воспроизведено)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Учётка роли SHIPPER_MANAGER. Реально воспроизведено на staging под ТК-приложением.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>1. Ввести телефон менеджера-грузоотправителя.
 2. Ввести его корректный пароль.
 3. Нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>ФАКТ (воспроизведено): сервер возвращает 403 wrong-app. Вход в приложение перевозчика запрещён — гейт по clientType (в TRANSPORT_COMPANY_APP пускается только TRANSPORT_ADMIN). Пользователь остаётся на экране входа с сообщением об ошибке.</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>mobile|rbac</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Роль SHIPPER_WAREHOUSE в carrier-app → 403 wrong-app</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Учётка склада SHIPPER_WAREHOUSE. Экран входа подтверждён вживую; фактический ответ по гейту clientType (проверить на устройстве).</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>1. Ввести телефон учётки склада.
 2. Ввести корректный пароль.
 3. Нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Вход в приложение перевозчика запрещён по гейту clientType (ожидается 403 wrong-app, как у SHIPPER_MANAGER). Пользователь остаётся на экране входа (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Вход отклонён гейтом clientType=TRANSPORT_COMPANY_APP (сервер 403 wrong-app), остаётся на экране входа. Проверено 2026-07-17: вход не выполнен; текст ошибки — generic «Непредвиденная ошибка. Попробуйте снова» вместо понятного wrong-app (→ BUG-029).</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>mobile|rbac</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Kirish →» неактивна при пустых полях</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа. Наблюдалось вживую: кнопка неактивна при пустых полях.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>1. Открыть экран входа, ничего не вводить — проверить кнопку.
 2. Ввести только телефон, пароль оставить пустым — проверить кнопку.
 3. Ввести только пароль, телефон оставить пустым — проверить кнопку.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>На шагах 1–3 кнопка «Kirish →» неактивна (не синяя, не нажимается). Активируется только когда заполнены оба поля.</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Показ/скрытие и очистка пароля</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа. В поле «Parol» справа наблюдались иконки крестик-очистка и глаз-показать.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>1. Ввести пароль в поле «Parol».
 2. Нажать иконку глаза — пароль отображается открытым текстом.
@@ -3563,634 +3526,634 @@
 4. Нажать крестик-очистку.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Глаз переключает видимость пароля туда-обратно. Крестик полностью очищает поле пароля; после очистки кнопка «Kirish →» снова неактивна.</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Телефон принимает ровно 9 цифр национального номера</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Открыт экран входа. Поле телефона: фиксированный флаг + «+998», плейсхолдер «00 000 00 00», 9 цифр.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>1. Начать вводить цифры в поле «Telefon raqam».
 2. Попробовать ввести буквы/символы.
 3. Ввести больше 9 цифр.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Префикс +998 фиксирован и не редактируется. Принимаются только цифры; ввод ограничен 9 цифрами (лишние не вводятся). Буквы/символы игнорируются.</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-010</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Слишком много попыток входа → 429 (rate limit)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Есть валидный телефон. Настроен лимит попыток на сервере (проверить на устройстве).</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>1. Несколько раз подряд быстро ввести неверный пароль и нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>После превышения лимита сервер отвечает 429; приложение показывает сообщение о временной блокировке/повторе позже, не крашится (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>После 5 неудачных попыток на телефон сервер отвечает 429; приложение показывает сообщение об ограничении. Проверено 2026-07-17: 429 срабатывает, но показан generic «Непредвиденная ошибка» вместо сообщения о лимите (→ BUG-029).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>mobile|network</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-013</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Happy path: отображение ленты доступных грузов</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход как TRANSPORT_ADMIN. Экран «Mavjud yuklar» подтверждён вживую (вкладка Buyurtmalar активна).</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>1. После входа дождаться загрузки вкладки «Buyurtmalar».
 2. Осмотреть заголовок «Mavjud yuklar» и список карточек грузов.
 3. Осмотреть нижнюю навигацию.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Показан заголовок «Mavjud yuklar», строка поиска и список карточек (PUBLISHED/QUOTED из обслуживаемых городов, sort по дате создания desc). Нижняя навигация: «Buyurtmalar» (активна), «Takliflar», «Profil». Грузы, по которым компания уже бидила, в ленте отсутствуют (живут во вкладке Takliflar).</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-014</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Состав карточки груза: номер, маршрут, дата, тип ТС, бейдж Avto</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>В ленте есть хотя бы один груз. Наблюдалось вживую.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>1. Рассмотреть карточку груза в ленте.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>На карточке: слева синяя точка + номер груза (наблюдались разные префиксы: NAMA-00011, UEIE-00026/25/24), справа бейдж типа транспорта «Avto». Строка маршрута «город отправления → город назначения». Внизу дата загрузки (2026-07-15) и иконка ТС с типом.</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-016</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Поиск по маршруту / ТК / ID</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>В ленте несколько грузов. Поле поиска «Marshrut, TC, ID bo'yicha qidirish...» подтверждено вживую.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>1. В строке поиска ввести часть номера груза (например «00011»).
 2. Очистить, ввести название города маршрута.
 3. Очистить, ввести несуществующую строку.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Лента фильтруется по совпадению (search матчит номер заказа и notes). По городу — грузы соответствующего маршрута. По несуществующей строке — пустой результат/пустое состояние. Очистка поиска возвращает полную ленту.</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-017</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Фильтрация ленты по обслуживаемым городам компании</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>У компании ограниченный список обслуживаемых городов (isAll=false). Серверный гейт fromOrToWarehouseIn.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>1. Просмотреть ленту грузов.
 2. Сверить города отправления/назначения карточек с обслуживаемыми компанией.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>В ленте видны только грузы, где origin ИЛИ destination входит в обслуживаемые города компании. Грузы полностью вне обслуживаемых городов не показываются.</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-018</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Компания обслуживает все города (isAll=true) — видит любой город</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>У компании isAll=true (обслуживает все города).</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>1. Просмотреть ленту грузов.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Показаны PUBLISHED/QUOTED-грузы всех городов (гейт по обслуживаемым городам снят). Прочие фильтры (уже бидили, ЧС складов, исключение) продолжают действовать.</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-019</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Груз со складом из ЧС компании скрыт из ленты</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>У компании есть склады в чёрном списке (blacklistWarehouseIds). Серверный гейт fromAndToWarehouseNotIn.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>1. Просмотреть ленту грузов.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Грузы, у которых склад отправления ИЛИ назначения в ЧС компании, в ленте отсутствуют.</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-020</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Компания исключена как бывший победитель — груз скрыт</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Заказ перевыпущен (CHANGED/REVERT), компания попала в excludedTransportCompanyId.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>1. Просмотреть ленту грузов.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Перевыпущенный груз скрыт от исключённого перевозчика (notExcludedForTransportCompany). При попытке подать оффер на такой груз сервер вернёт carrier-excluded.</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-021</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Пустое состояние ленты (нет доступных грузов)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Учётка, для которой нет ни одного PUBLISHED/QUOTED-груза в обслуживаемых городах.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>1. Открыть вкладку «Buyurtmalar».</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>После скелетонов загрузки показывается пустое состояние (нет карточек грузов), без бесконечного спиннера и без краша.</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-022</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Прокрутка и пагинация ленты</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>В ленте больше 20 грузов (страница по умолчанию size=20).</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>1. Прокрутить ленту вниз до конца первой страницы.
 2. Продолжить прокрутку.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Подгружается следующая страница грузов (бесконечная прокрутка/пагинация), сортировка по дате создания desc сохраняется, дубликатов карточек нет.</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-024</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Открытие деталей груза по тапу на карточку</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>В ленте есть груз. Переход подтверждён вживую.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть по карточке груза.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Открывается экран «Yuk tafsilotlari» выбранного груза (номер в шапке совпадает с карточкой).</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-025</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Детали груза «Yuk tafsilotlari»</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Happy path: состав экрана деталей</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Открыт груз из ленты. Экран подтверждён вживую.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть шапку (номер груза, «Yuk tafsilotlari», колокольчик, стрелка назад).
 2. Осмотреть карточку маршрута.
@@ -4198,146 +4161,146 @@
 4. Осмотреть кнопку внизу.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Показаны: шапка с номером (напр. NAMA-00011), карточка маршрута откуда→куда, секция спецификации со строками Transport (тип ТС), «Haydovchilar soni» (число водителей, напр. 1), «Uzunlik» (длина, 13.7 m), «Yuklash sanasi» (2026-07-15), «To'lov turi» (CNY). Внизу кнопка «Taklif yuborish».</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-027</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Детали груза «Yuk tafsilotlari»</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Тип оплаты в CNY по умолчанию</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Открыт груз. Наблюдалось вживую: «To'lov turi» = CNY.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>1. Посмотреть строку «To'lov turi» в спецификации.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Тип оплаты/валюта отображается как CNY (валюта наследуется от заказа). Далее в форме оффера поле цены будет с префиксом ¥ (CNY).</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-028</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Детали груза «Yuk tafsilotlari»</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Taklif yuborish» ведёт на форму оффера</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Открыт груз PUBLISHED/QUOTED, по которому компания ещё не бидила.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>1. Нажать «Taklif yuborish» внизу деталей.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Открывается форма оффера «Taklif yuborish» с номером того же груза и карточкой маршрута.</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-031</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Happy path: подача оффера с ценой (201, груз PUBLISHED→QUOTED на первом биде)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Груз PUBLISHED/QUOTED в scope, компания ещё не бидила и не исключена. Форма подтверждена вживую до конца подача не прокликана (проверить на устройстве).</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>1. На форме «Taklif yuborish» в поле «Sizning taklifingiz» (префикс ¥) ввести цену числовой клавиатурой.
 2. При необходимости заполнить «Dispetcher uchun izoh».
@@ -4345,833 +4308,833 @@
 4. Нажать «Yuborish».</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Оффер создаётся (сервер 201, статус PENDING, currency наследуется от заказа = CNY). Первый оффер на PUBLISHED-грузе переводит заказ PUBLISHED→QUOTED. Груз уходит из ленты «Mavjud yuklar» и появляется во вкладке «Takliflar/Yangi» (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Предложение цены отправлено (сервер 201), показано подтверждение, оффер в статусе PENDING, цена сохранена. Проверено 2026-07-17: подача оффера работает.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-032</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Yuborish» неактивна без цены</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Открыта форма оффера. Наблюдалось вживую: «Yuborish» неактивна, пока не введена цена.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>1. Оставить поле цены «Sizning taklifingiz» пустым.
 2. Заполнить только комментарий «Dispetcher uchun izoh».
 3. Проверить кнопку «Yuborish».</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Yuborish» остаётся неактивной, пока не введена цена. Комментарий сам по себе не активирует отправку.</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-033</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Валидация цены: 0 отклоняется</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Открыта форма оффера. Сервер: @Positive на price.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>1. В поле цены ввести 0.
 2. Попытаться отправить оффер.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Отправка отклоняется (клиентская валидация «цена &gt; 0» или сервер 400 @Positive по полю price). Показывается сообщение о некорректной цене; оффер не создаётся.</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-034</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Валидация цены: отрицательное значение отклоняется</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Открыта форма оффера. Сервер: @Positive.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>1. Попытаться ввести отрицательную цену (например -100).
 2. Отправить оффер.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Числовая клавиатура с префиксом ¥ не даёт ввести минус, либо отправка блокируется/сервер 400 @Positive. Оффер не создаётся.</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-035</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Валидация цены: нечисловой ввод/буквы не проходят</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Открыта форма оффера. Поле цены с числовой клавиатурой.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>1. Попытаться ввести буквы/несколько разделителей/пробелы в поле цены.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Поле принимает только корректное число (числовая клавиатура). Буквы и лишние разделители не вводятся; форма не отправляется с невалидным значением.</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-036</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Очень большая цена на PATCH-редактировании → риск 500 (нет DecimalMax)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Оффер уже подан (PENDING), выполняется редактирование. Серверный DRIFT: в OfferUpdateRequest нет @DecimalMax (в отличие от submit).</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Очень большая цена при PATCH-редактировании оффера</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Оффер уже подан (PENDING), выполняется редактирование. При PATCH-редактировании верхняя граница цены обрабатывается сервером как 409 (не 500).</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>1. Открыть редактирование своего PENDING-оффера.
 2. Ввести цену выше NUMERIC(15,2), напр. 10000000000000.00.
 3. Сохранить.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>⚠ РИСК: при submit (201-путь) верхняя граница проверяется (400 too-long), а при PATCH-редактировании граница НЕ проверяется — цена проходит валидацию и падает в 500/DataIntegrity на сохранении. Приложение должно ограничивать длину/значение на клиенте и корректно показывать ошибку, не крашась.</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Очень большая цена при редактировании оффера обрабатывается сервером как 409 Conflict (не 500). Приложение должно корректно показать ошибку, не крашась. (Проверено на backend: 1e15 → 409.)</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-037</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Дата загрузки readonly, комментарий необязателен</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Открыта форма оффера. Наблюдалось вживую.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>1. Попытаться изменить поле «Yuklash sanasi».
 2. Оставить «Dispetcher uchun izoh» пустым и отправить оффер с введённой ценой.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Поле «Yuklash sanasi» серое/readonly (2026-07-15), не редактируется. Комментарий «Dispetcher uchun izoh» необязателен — оффер отправляется без него.</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-038</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Bekor qilish» отменяет подачу</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Открыта форма оффера, введена цена. Наблюдалось вживую.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>1. Ввести цену.
 2. Нажать «Bekor qilish».</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Форма закрывается без создания оффера; возврат к деталям груза. Груз остаётся в ленте (оффер не подан).</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-039</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Повторная подача той же компанией → already-submitted</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>У компании уже есть активный оффер на этот груз (пара заказ+ТК уникальна).</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>1. Попытаться подать второй оффер на тот же груз (например через устаревшую карточку/deeplink).
 2. Ввести цену и нажать «Yuborish».</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Сервер 409, code=error.offer.already-submitted. Приложение показывает, что предложение уже отправлено; второй оффер не создаётся. В норме груз уже не должен быть в ленте (он во вкладке Takliflar).</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-040</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Груз больше не открыт для бидов → not-open-for-bids</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Груз к моменту отправки перешёл в статус вне PUBLISHED/QUOTED (SELECTED/IN_WORK/CANCELLED и т.п.).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>1. Открыть форму оффера по грузу, который тем временем закрылся для бидов.
 2. Ввести цену и нажать «Yuborish».</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Сервер 409, code=error.order.not-open-for-bids. Приложение показывает, что груз больше не принимает предложения; оффер не создаётся (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Заявка с выбранным победителем пропадает из ленты доступных у других перевозчиков — подать по ней оффер через UI нельзя (не видна). Ошибка not-open-for-bids — backend-подстраховка (при обращении по id). Проверено 2026-07-17: заявка исчезает из списка у других.</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-041</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Исключённый перевозчик подаёт оффер → carrier-excluded</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Компания исключена по этому заказу (excludedTransportCompanyId после перевыпуска тендера).</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>1. Попытаться подать оффер на перевыпущенный груз, где компания исключена.
 2. Нажать «Yuborish».</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Сервер 409, code=error.offer.carrier-excluded (проверяется до already-submitted). Оффер не создаётся; в норме такой груз скрыт из ленты (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Компания исключена по заказу (excludedTransportCompanyId после перевыпуска тендера): заказ скрыт из ленты перевозчика; прямой ре-бид → 409 error.offer.carrier-excluded. Проверено 2026-07-17: заказ NAMA-00019 отсутствует в ленте исключённого перевозчика (UI) + 409 по API.</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-042</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Редактирование оффера доступно только в статусе PENDING</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>У компании есть офферы в разных статусах (PENDING / SELECTED / REJECTED).</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>1. Открыть оффер в статусе PENDING → изменить цену/комментарий → сохранить.
 2. Открыть оффер в статусе SELECTED или REJECTED → попытаться изменить.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 1: правка сохраняется (200, currency не меняется). Шаг 2: редактирование недоступно/заблокировано; при попытке сервер 409 code=error.offer.not-editable. Приложение не даёт менять не-PENDING оффер (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Пока предложение в статусе PENDING — его можно отредактировать (новая цена сохраняется); в других статусах редактирование недоступно. Проверено 2026-07-17: изменение цены в PENDING сохраняется.</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-043</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Happy path: вкладки статусов со счётчиками</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. Вкладка «Takliflar» подтверждена вживую (у тест-аккаунта: Yangi 0, Tanlangan 0, Jarayonda 4).</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>1. Перейти на нижнюю вкладку «Takliflar».
 2. Осмотреть горизонтальные вкладки статусов и их счётчики.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Показаны горизонтально прокручиваемые вкладки: «Yangi» (новые), «Tanlangan» (выбранные), «Jarayonda» (в процессе), «Yo'lda» (в пути) — каждая со счётчиком. Значения соответствуют per-status сводке (feed/summary won-карта).</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-044</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Скелетоны загрузки сменяются контентом</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Открыта вкладка «Takliflar». Наблюдалось вживую: сначала скелетоны, затем контент/пустое состояние.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>1. Открыть/обновить вкладку «Takliflar».
 2. Понаблюдать за загрузкой.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Сначала показываются скелетоны загрузки, затем — либо список офферов, либо пустое состояние. Нет зависания на скелетонах.</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-045</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Пустое состояние «Faol takliflar yo'q» (вкладка Yangi)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Нет активных офферов в статусе Yangi. Подтверждено вживую.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>1. Открыть вкладку «Takliflar», выбрать статус «Yangi» (счётчик 0).</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Показана карточка с пунктирной рамкой и иконкой-конвертом, текст «Faol takliflar yo'q» и подсказка «Yukni oching va taklif yuboring — bu yerda paydo bo'ladi».</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-046</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Переключение между вкладками статусов</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Открыта вкладка «Takliflar», у аккаунта есть офферы в Jarayonda.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>1. Переключиться Yangi → Tanlangan → Jarayonda → Yo'lda.
 2. На каждой вкладке осмотреть содержимое.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Список фильтруется по выбранному статусу связанного заказа; счётчик вкладки совпадает с числом карточек. Jarayonda показывает выигранные грузы в работе (у тест-аккаунта 4).</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-047</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Карточка оффера открывает детали выигранного/поданного груза</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>На вкладке есть офферы. Детали остаются доступны даже вне PUBLISHED/QUOTED (bid != null).</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть по карточке оффера (например в Jarayonda).</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Открываются детали груза с заполненными полями активного бида (сумма/комментарий). Для выигранного груза (Tanlangan/Jarayonda) доступны действия по водителям.</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-048</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Назначение водителя на выигранный груз (Tanlangan/Jarayonda)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Есть выигранный груз в статусе SELECTED (Tanlangan). Водитель свободен, с cardId, той же компании. Проверить на устройстве (ветка не прокликана до конца).</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>1. Открыть выигранный груз во вкладке Tanlangan.
 2. Перейти к назначению водителей.
@@ -5179,831 +5142,831 @@
 4. Сохранить назначение.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Водитель прикрепляется к заказу (200), указывается госномер. Доступно назначение до driversCount водителей. Возможные ошибки сервера: busy-on-another-order (водитель занят), plate-busy (номер занят на другом активном заказе), blacklisted (в ЧС шиппера), card-id-required (нет ID-карты). Проверить на устройстве.</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Водитель прикрепляется к выигранному грузу (сохраняется без ошибки), виден на карточке груза. Проверено 2026-07-17: назначение водителя работает.</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-049</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Старт работы по грузу (SELECTED→IN_WORK) при полном комплекте водителей</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Выигранный груз SELECTED, прикреплено &gt;= driversCount водителей. Проверить на устройстве.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>1. Открыть выигранный груз с назначенными водителями.
 2. Нажать кнопку старта работы.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Заказ переходит SELECTED→IN_WORK (Ishda), груз перемещается на вкладку «Jarayonda». Если водителей недобор — сервер 409 drivers-incomplete, старт заблокирован. Проверить на устройстве.</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>При полном комплекте водителей груз переходит SELECTED→IN_WORK (старт работает). Проверено 2026-07-20: назначение всех водителей и старт работают. Примечание: при НЕполном комплекте (1 из 2) приложение показывает вводящее в заблуждение сообщение (→ BUG-030), но функционально всё ок.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-050</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Замена/отцепление водителя на выигранном грузе</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Выигранный груз SELECTED/IN_WORK с назначенным водителем. Проверить на устройстве.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>1. Открыть выигранный груз.
 2. Заменить назначенного водителя на другого свободного (или отцепить).</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Замена: старый водитель освобождается, новый прикрепляется (200). Отцепление: в SELECTED можно убрать всех; в IN_WORK нельзя убрать последнего (сервер 409 must-keep-driver). Проверить на устройстве.</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Замена/отцепление водителя на выигранном грузе работает: новый водитель встаёт на место (в SELECTED можно до нуля; в IN_WORK нельзя убрать последнего). Проверено 2026-07-20: замена функционально работает. Примечания: неверный текст ошибки (→ BUG-030) и уже-назначенный водитель в списке кандидатов (→ BUG-031).</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-051</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Список офферов отсортирован новыми сверху; офферы удалённых грузов скрыты</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>У компании несколько офферов, часть по удалённым заказам.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>1. Открыть вкладку «Takliflar».
 2. Оценить порядок карточек и отсутствие «мёртвых» грузов.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Офферы отсортированы по дате создания desc (новые первыми). Офферы по удалённым/неживым заказам не показываются (orderLive-фильтр).</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-052</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Happy path: шапка профиля ТК</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Выполнен вход. Экран профиля подтверждён вживую.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>1. Перейти на вкладку «Profil».
 2. Осмотреть карточку-шапку.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>Показана карточка с меткой «TRANSPORT KOMPANIYASI», ФИО пользователя (напр. «Begimbaev Naurizbek …»), названием компании (напр. «Naurizbek Trucks») и аватаром-инициалами (BN).</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-053</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Плитки статистики mavjud/kutilmoqda/jarayonda</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Открыт профиль. Плитки подтверждены вживую (472 mavjud, 187 kutilmoqda, 1 jarayonda).</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть три плитки статистики под шапкой.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Показаны три плитки: «… mavjud» (доступно), «… kutilmoqda» (ожидается), «… jarayonda» (в процессе). Значения соответствуют серверной сводке feed/summary (marketplace/won). Числа согласуются со счётчиками вкладки Takliflar.</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-054</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Пункт «Bildirishnomalar» с бейджем непрочитанных</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Открыт профиль. Пункт подтверждён вживую (красный бейдж «2»).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть пункт «Bildirishnomalar».
 2. Тапнуть по нему.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Пункт «Bildirishnomalar» показывает бейдж числа непрочитанных (2). По тапу открывается экран уведомлений; после просмотра бейдж должен сбрасываться (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Пункт уведомлений открывает список; тап делает уведомление прочитанным (из списка не пропадает — норм), бейдж уменьшается. Проверено 2026-07-20: функционально работает. Минус: содержимое уведомлений на китайском, не локализовано (→ BUG-032).</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-056</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Переход в «Avtopark» из профиля</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Открыт профиль. Пункт «Avtopark» подтверждён вживую (значение «7 haydovchi»).</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>1. Тапнуть пункт «Avtopark» (показывает число водителей).</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Открывается экран «Avtopark» со списком водителей компании. Число водителей в пункте профиля согласуется со списком.</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-057</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Выход из аккаунта «Chiqish»</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Открыт профиль. Кнопка «Chiqish» (красная) подтверждена вживую.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>1. Нажать «Chiqish».
 2. Подтвердить выход (если есть диалог).</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Сессия завершается, приложение возвращает на экран входа «Yana xush kelibsiz». Повторный вход требует ввода телефона и пароля. Данные предыдущей учётки не отображаются (проверить наличие диалога подтверждения на устройстве).</t>
-        </is>
-      </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>«Chiqish» выполняет выход — возврат на экран входа, повторный вход возможен. Проверено 2026-07-20: выход работает. Замечание: нет диалога подтверждения выхода (→ BUG-033).</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>mobile|session</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-058</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Версия приложения в подвале</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Открыт профиль. Подвал подтверждён вживую.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>1. Прокрутить профиль вниз до подвала.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Показана строка версии «Manzil-TC v1.0 · Build 2026.05».</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-059</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Happy path: список водителей компании</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Открыт «Avtopark». Экран подтверждён вживую.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>1. Осмотреть шапку «Avtopark» со стрелкой назад.
 2. Осмотреть строку поиска и список карточек водителей.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Показан список карточек: аватар-инициалы, имя, код «NAMA-xxxxx», телефон, справа красная иконка-корзина. Внизу кнопка «+ Haydovchi qo'shish». Список — только водители своей компании (sort по дате создания desc).</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-060</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Поиск водителя по ФИО / номеру / телефону</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>В автопарке несколько водителей. Поле «F.I.O., raqam, tel bo'yicha qidirish...» подтверждено вживую.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>1. Ввести часть ФИО водителя.
 2. Очистить, ввести часть телефона.
 3. Ввести несуществующую строку.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Список фильтруется по совпадению имени/телефона. По несуществующей строке — пустой результат. Очистка поиска возвращает полный список.</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-063</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Удаление водителя из списка (красная корзина) — диалог подтверждения</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Удаление водителя из списка (красная корзина)</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Открыт «Avtopark», водитель свободен (не на активном заказе). Красная корзина прямо в карточке — риск случайного удаления. Проверить на устройстве.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>1. Нажать красную корзину на карточке свободного водителя.
 2. Проверить, появляется ли диалог подтверждения.
 3. Подтвердить удаление.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Ожидается диалог подтверждения перед удалением (защита от случайного тапа). При подтверждении свободный водитель удаляется (сервер 204, soft-delete), карточка исчезает из списка, число в профиле уменьшается. ⚠ Проверить наличие подтверждения на устройстве — если его нет, это дефект UX (риск потери водителя одним тапом).</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Показывается диалог подтверждения перед удалением (защита от случайного тапа). При подтверждении свободный водитель удаляется (сервер 204, soft-delete), карточка исчезает из списка, число в профиле уменьшается.</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-064</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Удаление занятого водителя → busy-cannot-delete</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Водитель прикреплён к активному заказу (SELECTED/IN_WORK/IN_TRANSIT).</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>1. Нажать красную корзину на карточке занятого водителя.
 2. Подтвердить удаление (если есть диалог).</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Удаление отклоняется: сервер 409, code=error.driver.busy-cannot-delete. Приложение показывает, что водитель занят на заказе и не может быть удалён; карточка остаётся в списке (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Удаление занятого водителя (на активном заказе) отклоняется (busy-cannot-delete), водитель остаётся в списке. Проверено 2026-07-20: занятого водителя удалить нельзя.</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-065</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Отмена удаления в диалоге подтверждения</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Открыт «Avtopark», нажата корзина у водителя, показан диалог. Проверить на устройстве.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>1. Нажать корзину у водителя.
 2. В диалоге подтверждения нажать «Отмена/Bekor qilish».</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Удаление отменяется, водитель остаётся в списке без изменений (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Диалог подтверждения удаления появляется; после «Отмена» водитель не удаляется. Проверено 2026-07-20: отмена работает. Замечание: диалог удаления на узбекском при русском UI (→ BUG-034).</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-066</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Кнопка «+ Haydovchi qo'shish» открывает форму добавления</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Открыт «Avtopark». Кнопка подтверждена вживую.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>1. Нажать «+ Haydovchi qo'shish» внизу экрана.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Открывается форма «Yangi haydovchi» с полями «To'liq ism», «Telefon raqam», «ID karta raqami» и кнопками «Bekor qilish»/«Saqlash».</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-067</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Пустой автопарк (у компании нет водителей)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Учётка без водителей.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>1. Открыть «Avtopark».</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Показан пустой список (без карточек), кнопка «+ Haydovchi qo'shish» доступна. Без краша и бесконечного спиннера (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Пустой автопарк показывает пустое состояние («Водителей нет / Добавьте первого водителя») с иллюстрацией; приложение не падает. Проверено 2026-07-20: пустое состояние показано, локализовано (русский).</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-068</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Happy path: создание водителя (имя + телефон + ID-карта)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Открыта форма «Yangi haydovchi». Форма подтверждена вживую (создание до конца не прокликано — проверить на устройстве).</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>1. В поле «To'liq ism» ввести полное имя.
 2. В поле «Telefon raqam» ввести номер (+998, 9 цифр).
@@ -6011,611 +5974,611 @@
 4. Нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Водитель создаётся (сервер 201), привязан к компании, статус — свободен, 0 завершённых заказов. Возврат в «Avtopark», новый водитель появляется в списке, число водителей в профиле увеличивается (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Создание водителя (ФИО + телефон + ID-карта) сохраняется без ошибки, водитель появляется в списке автопарка. Проверено 2026-07-20: создание работает.</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-069</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Валидация: пустое имя «To'liq ism» → required</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Открыта форма. Сервер: @NotBlank + @Size(min=2) на fullName.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>1. Оставить «To'liq ism» пустым.
 2. Заполнить телефон.
 3. Нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>Сохранение блокируется: обязательное поле имени. Показывается ошибка «обязательно» (сервер 400, field=fullName). Водитель не создаётся.</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-070</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Валидация: имя из 1 символа → too-short (границы 2..255)</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Открыта форма. Сервер: @Size(min=2,max=255) на fullName.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>1. Ввести имя из 1 символа.
 2. Заполнить телефон и сохранить.
 3. Повторить с именем из 2 символов.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>1 символ — отклоняется (400, @Size min=2). 2 символа — принимается. Приложение показывает ошибку длины на слишком коротком имени.</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-071</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Валидация: пустой телефон → required</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Открыта форма. Сервер: @NotBlank на phone.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>1. Заполнить имя.
 2. Оставить «Telefon raqam» пустым.
 3. Нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>Сохранение блокируется: телефон обязателен (сервер 400, field=phone). Водитель не создаётся.</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-072</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Валидация формата телефона (E.164 +[10..15] цифр)</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Открыта форма. Поле телефона с префиксом +998. Сервер: @Pattern ^\+[0-9]{10,15}$.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>1. Ввести слишком короткий номер (меньше 9 нац. цифр).
 2. Попытаться ввести буквы/символы.
 3. Сохранить.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Слишком короткий/невалидный номер отклоняется (клиентская маска и/или сервер 400 @Pattern, field=phone). Буквы не вводятся. Валидный узбекский номер (+998 + 9 цифр = 12 знаков) проходит.</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-073</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Дубликат телефона в компании → phone-exists</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>В компании уже есть водитель с таким телефоном. Сервер: existsByTransportCompanyIdAndPhone.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>1. Ввести имя и телефон, уже занятый другим водителем компании.
 2. Нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>Создание отклоняется: сервер 409, code=error.driver.phone-exists. Приложение показывает, что водитель с таким номером уже существует; дубликат не создаётся.</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-074</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>ID-карта необязательна при создании; нужна при назначении</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Открыта форма. Сервер: cardId опционален при создании (@Size max=32), но требуется при прикреплении к заказу.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>1. Заполнить имя и телефон, поле «ID karta raqami» оставить пустым.
 2. Сохранить.
 3. Позже попытаться назначить этого водителя на выигранный груз без cardId.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 1–2: водитель создаётся без ID-карты (201, cardId=null). Шаг 3: при назначении без cardId сервер вернёт 400 card-id-required — потребуется указать ID-карту в момент назначения (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>ID-карта необязательна при создании водителя (сохраняется без неё), но требуется при назначении на груз (просят ввести / card-id-required). Проверено 2026-07-20: без ID-карты сохраняется; при назначении ID-карту требуют. Примечание: форма добавления на узбекском при русском UI (→ BUG-034).</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-075</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Граница длины ID-карты (max 32 символа)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Открыта форма. Сервер: @Size(max=32) на cardId.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>1. Ввести ID-карту длиной 32 символа и сохранить.
 2. Ввести ID-карту длиной 33 символа и сохранить.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>32 символа — принимается (201). 33 символа — отклоняется (400, @Size max=32, too-long). Приложение ограничивает длину/показывает ошибку.</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-076</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Кнопка «Bekor qilish» отменяет создание</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Открыта форма, частично заполнена.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>1. Заполнить часть полей.
 2. Нажать «Bekor qilish».</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>Форма закрывается без создания водителя; возврат в «Avtopark», список без изменений.</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-077</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Защита от двойного тапа по «Saqlash»</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Открыта форма, поля валидны.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>1. Заполнить валидные данные.
 2. Быстро дважды нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Создаётся ровно один водитель (кнопка блокируется на время запроса). Дубликат не создаётся; повторный запрос не даёт второго водителя (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Двойной быстрый тап по «Saqlash» создаёт только одного водителя (без дубля); кнопка блокируется после первого тапа. Проверено 2026-07-20: кнопка становится неактивной после первого нажатия, дубля нет.</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>mobile|network</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-079</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Двойной тап по «Yuborish» при подаче оффера</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Открыта форма оффера, введена цена.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>1. Ввести цену.
 2. Быстро дважды нажать «Yuborish».</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Создаётся ровно один оффер (кнопка блокируется/идемпотентность). Второй запрос не создаёт дубль — при гонке сервер вернёт already-submitted, обрабатывается без краша (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Двойной быстрый тап по «Yuborish» создаёт только одно предложение (без дубля); кнопка блокируется после первого тапа. Проверено 2026-07-20: дубля нет, кнопка блокируется.</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>mobile|network</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-080</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Сворачивание в фон и возврат сохраняют состояние</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Открыт любой экран (например форма оффера с введённой ценой).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>1. Свернуть приложение (Home), открыть другое приложение.
 2. Вернуться в приложение перевозчика.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Приложение восстанавливает предыдущий экран и введённые данные (или корректно перезагружает список). Сессия жива, повторный вход не требуется. Нет краша при возврате (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Сворачивание в фон и возврат сохраняют состояние: приложение возвращается на тот же экран, введённое не потеряно, не выкидывает на старт/логин. Проверено 2026-07-20: возвращается на то же место.</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>mobile|session</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>MOB-CR-084</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Навигация назад системной кнопкой Android</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Открыт вложенный экран (детали груза / форма оффера / добавление водителя).</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>1. Открыть форму оффера с введённой ценой.
 2. Нажать системную кнопку «Назад» Android.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Системная «Назад» ведёт себя как «Bekol qilish»/стрелка назад — возврат на предыдущий экран без отправки оффера. На корневых вкладках «Назад» не закрывает приложение неожиданно/предупреждает о выходе (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Системная кнопка «Назад» Android возвращает на предыдущий экран пошагово (не закрывает приложение сразу, не выкидывает на логин); с главного экрана — обычное поведение. Проверено 2026-07-20: навигация назад работает.</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>mobile|session</t>
         </is>

--- a/docs/testcases/manzil-mobile-testcases.xlsx
+++ b/docs/testcases/manzil-mobile-testcases.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,16 +95,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -472,13 +492,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -499,59 +520,79 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Слой</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Кейсов</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Warehouse-app</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Склад</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Логин · создание заявки · адрес (cityId) · публикация · lifecycle · связь · goods-sent</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Carrier-app</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Перевозчик</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Логин · лента · предложение · водители · назначение · старт заявки</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>119</v>
       </c>
     </row>
@@ -634,2529 +675,2526 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Happy path: вход по телефону (9 цифр) и паролю без OTP</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Приложение склада установлено, смотрит на staging. Есть рабочая учётка SHIPPER_WAREHOUSE (+998900000004 / &lt;staging-password&gt;)</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть приложение
-2. Дождаться экрана входа с логотипом MANZIL и подписью «Hisobingizga kiring»
-3. Тапнуть поле телефона (плейсхолдер «00 000 00 00»)
-4. Ввести национальный номер 900000004 (9 цифр)
-5. Тапнуть поле «Parol», ввести пароль
-6. Нажать «Kirish»</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Вход успешен. Открывается главный экран «Buyurtmalar» со списком заявок и зелёной FAB «Ariza yaratish». Нижняя навигация Buyurtmalar/Profil видна</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Приложение склада установлено на Android-устройстве и подключено к тестовому стенду (staging). Есть рабочая учётная запись сотрудника склада: телефон +998900000004, пароль тестового стенда известен.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть приложение склада.
+2. Дождаться экрана входа с логотипом MANZIL и подписью «Hisobingizga kiring» (войдите в аккаунт).
+3. Нажать поле телефона (плейсхолдер «00 000 00 00») и ввести 900000004 — 9 цифр без кода страны.
+4. Нажать поле «Parol» и ввести пароль.
+5. Нажать кнопку «Kirish» (Войти).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Вход выполняется без запроса кода из СМС. Открывается главный экран «Buyurtmalar» (Заявки) со списком заявок и зелёной круглой кнопкой «+» (Ariza yaratish — создать заявку). Внизу видна панель навигации с пунктами «Buyurtmalar» и «Profil».</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Кнопка «Kirish» неактивна при пустых полях</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>1. Не заполнять поля
-2. Оценить состояние кнопки «Kirish»
-3. Заполнить только телефон — оценить кнопку
-4. Заполнить только пароль (телефон пуст) — оценить кнопку</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Пока оба поля не заполнены, кнопка «Kirish» бледная/неактивная и не реагирует на тап. Синей (активной) становится только когда заполнены и телефон, и пароль</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа приложения склада, поля телефона и пароля пустые.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Ничего не вводить и посмотреть на кнопку «Kirish».
+2. Заполнить только поле телефона — снова посмотреть на кнопку.
+3. Очистить телефон и заполнить только поле «Parol» — снова посмотреть на кнопку.
+4. Заполнить оба поля.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Пока заполнены не оба поля, кнопка «Kirish» бледная (неактивная) и на нажатие не реагирует. Синей (активной) она становится только после заполнения и телефона, и пароля.</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>mobile|validation|negative</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Неверный пароль → ошибка «Noto'g'ri login yoki parol» (401)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа. Известен валидный телефон</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести валидный телефон 900000004
-2. Ввести заведомо неверный пароль
-3. Нажать «Kirish»</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Вход отклонён (сервер 401 error.invalid-credentials). Показан узбекский текст «Noto'g'ri login yoki parol». Пользователь остаётся на экране входа, поля сохранены</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа. Известен телефон действующего сотрудника склада (900000004).</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести телефон 900000004.
+2. Ввести заведомо неверный пароль.
+3. Нажать «Kirish».</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Вход не выполняется: появляется сообщение «Noto'g'ri login yoki parol» (неверный логин или пароль). Пользователь остаётся на экране входа, введённые значения в полях сохраняются.</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|validation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Чужая роль/среда → 403 wrong-app, остаётся на входе</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа. Есть учётка НЕ SHIPPER_WAREHOUSE (напр. SHIPPER_MANAGER +998900000003)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести телефон 900000003 и его корректный пароль
-2. Нажать «Kirish»</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Вход отклонён гейтом clientType=WAREHOUSE_APP (сервер 403 wrong-app): пользователь остаётся на экране входа, внутрь не пускает. Проверено 2026-07-17: отказ работает; текст ошибки сейчас английский generic «Access denied» вместо локализованного узбекского сообщения (→ BUG-028).</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа приложения склада. Есть учётная запись с другой ролью, не «Сотрудник склада» — например, Менеджер с телефоном +998900000003 и известным паролем.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести телефон 900000003 и его правильный пароль.
+2. Нажать «Kirish».</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Вход отклоняется: приложение склада пускает только сотрудников склада. Пользователь с другой ролью остаётся на экране входа, внутрь не попадает, показывается сообщение об отказе в доступе; правильным поведением считается локализованный текст этого сообщения. Проверено 2026-07-17: отказ работает; текст ошибки сейчас английский generic «Access denied» вместо локализованного узбекского сообщения (→ BUG-028).</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>mobile|rbac|negative</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Показ/скрытие пароля иконкой-глаз</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести пароль в поле «Parol» (по умолчанию точечная маскировка)
-2. Тапнуть иконку-глаз
-3. Тапнуть иконку-глаз повторно</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>По умолчанию пароль скрыт точками. После тапа по глазу пароль отображается открытым текстом. Повторный тап снова маскирует</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести любой пароль в поле «Parol».
+2. Нажать иконку-глаз в поле пароля.
+3. Нажать иконку-глаз повторно.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>По умолчанию введённый пароль скрыт точками. После первого нажатия на глаз пароль показывается открытым текстом, после повторного — снова скрывается точками.</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Поле телефона: фиксированный +998, ввод 9 национальных цифр с маской</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>1. Оценить префикс поля телефона
-2. Начать вводить цифры номера
-3. Попробовать ввести больше 9 цифр
-4. Попробовать ввести буквы/символы</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Слева зафиксированы флаг и «+998» (стрелка-dropdown рядом). Ввод только национальной части — 9 цифр с маской «99 474 60 06». Свыше 9 цифр не принимается; буквы не вводятся. Проверено вручную 2026-07-17: лимит 9 цифр и запрет букв работают.</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть поле телефона.
+2. Начать вводить цифры номера.
+3. Попробовать ввести десятую цифру.
+4. Попробовать ввести буквы и символы.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Слева в поле зафиксированы флаг и код «+998», рядом стрелка выпадающего списка. Вводится только национальная часть номера — 9 цифр с маской вида «99 474 60 06». Десятая цифра в поле не появляется; буквы и символы не вводятся. Проверено вручную 2026-07-17: лимит 9 цифр и запрет букв работают.</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-008</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Системный диалог разрешения на уведомления при первом запуске</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Свежая установка приложения (clearState), Android 13+</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>1. Впервые запустить приложение
-2. Дождаться системного диалога Android «Allow notifications?»
-3. Проверить оба варианта (Allow / Don't allow) на отдельных прогонах</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Показан системный диалог уведомлений. Выбор «Allow» или «Don't allow» не блокирует вход — экран входа доступен после закрытия диалога</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Приложение склада только что установлено (первый запуск, данные приложения чистые). Устройство на Android 13 или новее.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Запустить приложение впервые.
+2. Дождаться системного диалога Android «Allow notifications?».
+3. В одном прогоне выбрать «Allow», в другом (после переустановки приложения) — «Don't allow».</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>При первом запуске появляется системный диалог разрешения уведомлений. Любой выбор («Allow» или «Don't allow») не блокирует работу: после закрытия диалога открывается экран входа.</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-010</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Экран входа</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Лимит попыток входа: 5 неудач/телефон → 429</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа. Тест проводить осторожно (лимитер: 5 неудач/телефон, 30/IP, окно 10 мин)</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести валидный телефон и неверный пароль
-2. Нажать «Kirish»
-3. Повторить неверный вход 5 раз подряд для одного телефона</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>После 5 неудачных попыток на телефон сервер отвечает 429; приложение показывает сообщение об ограничении. Проверено 2026-07-17: после 5 попыток появляется «Too many requests» (429 работает). Текст английский, не локализован (→ BUG-028).</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа. Учесть серверное ограничение: 5 неудачных попыток на один телефон (и 30 на один IP-адрес) в окне 10 минут — тест выполнять аккуратно, чтобы не заблокировать другие проверки.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести валидный телефон и заведомо неверный пароль.
+2. Нажать «Kirish».
+3. Повторить неудачный вход 5 раз подряд с тем же телефоном.
+4. Попробовать войти ещё раз.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>После 5 неудачных попыток по одному телефону очередные попытки блокируются: вход не выполняется, приложение показывает сообщение об ограничении числа попыток. Проверено 2026-07-17: после 5 попыток появляется «Too many requests» (429 работает). Текст английский, не локализован (→ BUG-028).</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|session</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-013</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Вкладки статусов со счётчиками отображаются</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход, открыт список заявок</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть верхнюю ленту вкладок статусов
-2. Сверить набор вкладок и счётчики</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Видны вкладки со счётчиками: «E'lon qilindi» [PUBLISHED], «Olingan» [взятые], «Ishda» [IN_WORK], «Yo'lda» [IN_TRANSIT], «Tugallangan» [COMPLETED]. Счётчик у вкладки соответствует числу заявок в статусе (сверить с /orders/summary)</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход сотрудником склада, открыт список заявок «Buyurtmalar». Есть заявки в разных статусах.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть ленту вкладок статусов над списком.
+2. Открыть каждую вкладку и сравнить число в её счётчике с фактическим количеством заявок в списке.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Видны вкладки со счётчиками: «E'lon qilindi» (опубликованные), «Olingan» (взятые), «Ishda» (в работе), «Yo'lda» (в пути), «Tugallangan» (завершённые). Число в счётчике каждой вкладки совпадает с количеством заявок в её списке.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|state</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-014</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Горизонтальная прокрутка ленты вкладок к «Tugallangan»</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. Много заявок → вкладки переполняют строку</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>1. Заметить, что крайняя вкладка «Tugallangan» уходит за правый край
-2. Свайпнуть ленту вкладок влево
-3. Тапнуть вкладку «Tugallangan»</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Лента вкладок горизонтально прокручивается, «Tugallangan» становится видимой и открывается. Крайние левые вкладки не должны пропадать без прокрутки</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход. Вкладок статусов больше, чем помещается на экране: крайняя «Tugallangan» уходит за правый край.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Убедиться, что вкладка «Tugallangan» не видна целиком.
+2. Смахнуть ленту вкладок влево.
+3. Нажать вкладку «Tugallangan».</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Лента вкладок прокручивается по горизонтали: «Tugallangan» становится видимой и открывается по нажатию. Крайние левые вкладки при этом не пропадают — к ним можно вернуться прокруткой вправо.</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|state</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-015</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Переключение между вкладками фильтрует список по статусу</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. Есть заявки в разных статусах</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть вкладку «E'lon qilindi» — оценить список
-2. Тапнуть «Ishda» — оценить список
-3. Тапнуть «Yo'lda» — оценить список</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Список перерисовывается под выбранный статус. На вкладке «E'lon qilindi» показываются PUBLISHED (включая свёрнутые QUOTED). CANCELLED/SUPERSEDED нигде не отображаются</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход. Есть заявки в разных статусах.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать вкладку «E'lon qilindi» и осмотреть список.
+2. Нажать вкладку «Ishda» и осмотреть список.
+3. Нажать вкладку «Yo'lda» и осмотреть список.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>При каждом переключении список перестраивается и показывает только заявки в статусе выбранной вкладки. На «E'lon qilindi» видны опубликованные заявки, в том числе те, по которым перевозчики уже прислали предложения (отдельной вкладки для них нет). Отменённые и заменённые при повторной публикации заявки не отображаются ни на одной вкладке.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|state|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-016</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Содержимое карточки заявки: номер, дата, маршрут, тип ТС</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. На вкладке есть заявки</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>1. Рассмотреть карточку заявки
-2. Сверить отображаемые поля</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Карточка показывает: номер вида «NAMA-00010» (staging-префикс NAMA), дату загрузки, блок маршрута — зелёная точка = отправление (город/склад), стрелка ---&gt;, красная метка = назначение, чип типа ТС «Bortli 13.7». Маршруты реальные CN↔CIS (Urumqi, Yiwu, Nukus, Almata, Beijing)</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход. На открытой вкладке есть хотя бы одна заявка.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Рассмотреть карточку заявки в списке.
+2. Сверить набор отображаемых полей.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>На карточке видны: номер вида «NAMA-00010» (на тестовом стенде номера начинаются с NAMA), дата загрузки, блок маршрута — зелёная точка с пунктом отправления (город/склад), стрелка к красной метке с пунктом назначения, а также чип типа ТС (например «Bortli 13.7»). Маршруты — реальные направления Китай↔СНГ: Urumqi, Yiwu, Beijing, Nukus, Almata.</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-017</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Пустой тип ТС отображается как «—»</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. Есть заявка без типа ТС (напр. NAMA-00009 Nukus→Almata)</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>1. Найти карточку заявки без типа транспорта
-2. Осмотреть чип типа ТС</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>У части заявок чип типа ТС пуст и показывает «—» (вероятно легаси-данные; по API vehicleTypeId обязателен при создании). Ожидается осмысленный плейсхолдер вместо «—».</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход. В списке есть заявка без типа ТС (например NAMA-00009, маршрут Nukus→Almata).</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Найти в списке карточку заявки без типа транспорта.
+2. Осмотреть чип типа ТС на карточке.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Чип типа ТС у такой заявки показывает прочерк «—», приложение при этом работает без сбоев. Это старые данные: при создании новой заявки тип ТС обязателен, поэтому у новых заявок прочерка быть не должно. Правильным поведением считается осмысленная подпись вместо голого «—».</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|state</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-018</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Пустое состояние вкладки без заявок</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. Есть вкладка со счётчиком 0 (напр. «Yo'lda (0)»)</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть вкладку без заявок</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Список пуст, показано пустое состояние с текстом (напр. «Пока нет заказов»). Приложение не падает, нет бесконечного лоадера. Проверено 2026-07-17: пустое состояние показано, текст локализован.</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход. Есть вкладка со счётчиком 0 (например «Yo'lda (0)»).</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть вкладку, на которой нет заявок.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Список пуст, показано пустое состояние с поясняющим текстом (например «Пока нет заказов»). Приложение не падает, бесконечный индикатор загрузки не крутится. Проверено 2026-07-17: пустое состояние показано, текст локализован.</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|state</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-019</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Главный экран (Buyurtmalar)</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Открытие деталей заявки по тапу на карточку</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. На вкладке есть заявка</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть по карточке заявки</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Открывается экран деталей выбранной заявки (секции, статусная лента). Данные соответствуют карточке (маршрут, дата, тип ТС)</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход. На открытой вкладке есть заявка.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать на карточку заявки.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Открывается экран деталей именно этой заявки: секции с данными и статусная лента. Данные совпадают с карточкой из списка — маршрут, дата, тип ТС.</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-021</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Выбор типа транспорта (Transport turini tanlang)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Открытие шага выбора транспорта по FAB, «Avtomobil» активен</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход, открыт список заявок</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>1. Нажать зелёную FAB «+» (Ariza yaratish)
-2. Дождаться bottom sheet «Transport turini tanlang»
-3. Оценить карточки «Temir yo'l» и «Avtomobil»</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Открывается bottom sheet с заголовком «Transport turini tanlang». Карточка «Avtomobil» активна (выделена зелёным). Карточка «Temir yo'l» серая/недоступна</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, открыт список заявок.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать зелёную круглую кнопку «+» (Ariza yaratish).
+2. Дождаться появления нижней шторки «Transport turini tanlang» (выбор типа транспорта).
+3. Осмотреть карточки «Temir yo'l» и «Avtomobil».</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Снизу открывается шторка с заголовком «Transport turini tanlang». Карточка «Avtomobil» активна и выделена зелёным; карточка «Temir yo'l» серая, выглядит недоступной.</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-022</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Выбор типа транспорта (Transport turini tanlang)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>«Temir yo'l» недоступен для выбора</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Открыт bottom sheet «Transport turini tanlang»</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть по серой карточке «Temir yo'l»</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Выбор не срабатывает, переход к форме не происходит. Ж/д тип недоступен (в разработке). Форма создания открывается только для «Avtomobil»</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Открыта шторка «Transport turini tanlang».</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать на серую карточку «Temir yo'l».</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Нажатие не срабатывает: выбор не происходит, форма создания заявки не открывается. Железнодорожный тип пока недоступен (функциональность в разработке) — форма создания открывается только для «Avtomobil».</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-023</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Выбор типа транспорта (Transport turini tanlang)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Выбор «Avtomobil» открывает форму «Yangi ariza yaratish»</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Открыт bottom sheet «Transport turini tanlang»</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть «Avtomobil»</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Открывается форма «Yangi ariza yaratish» с полями: Yuklash sanasi, Transport (чипы), Haydovchilar soni, Yo'nalish, Izohlar. Внизу «Orqaga» / «Ko'rib chiqish». cargoType=AUTO</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Открыта шторка «Transport turini tanlang».</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать карточку «Avtomobil».</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Открывается форма «Yangi ariza yaratish» (новая заявка) с полями: «Yuklash sanasi» (дата загрузки), «Transport» (чипы типов ТС), «Haydovchilar soni» (число водителей), «Yo'nalish» (маршрут), «Izohlar» (комментарии). Внизу кнопки «Orqaga» (назад) и «Ko'rib chiqish» (предпросмотр).</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-024</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Дата загрузки по умолчанию = сегодня</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма «Yangi ariza yaratish»</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть поле «Yuklash sanasi *»
-2. Сверить значение по умолчанию</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Поле «Yuklash sanasi» с иконкой-календарём предзаполнено сегодняшней датой (напр. «10 Iyul · Ju»). Дата в зоне Asia/Tashkent</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi ariza yaratish».</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть поле «Yuklash sanasi *».
+2. Сравнить предзаполненное значение с сегодняшней датой.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Поле «Yuklash sanasi» с иконкой календаря уже заполнено сегодняшней датой (например «10 Iyul · Ju»). Дата соответствует сегодняшнему дню по времени Ташкента.</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-025</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Выбор даты загрузки через календарь (будущая дата)</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма «Yangi ariza yaratish»</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть поле «Yuklash sanasi»
-2. Открыть календарь
-3. Выбрать будущую дату (напр. +3 дня)
-4. Подтвердить</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Календарь открывается, выбранная будущая дата подставляется в поле. Даты в прошлом недоступны в календаре либо при публикации отклоняются сервером (error.order.load-not-after-publish).</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi ariza yaratish».</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать поле «Yuklash sanasi».
+2. В открывшемся календаре выбрать будущую дату (например +3 дня).
+3. Подтвердить выбор.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Календарь открывается, выбранная будущая дата подставляется в поле. Прошедшие даты выбрать нельзя — они недоступны в календаре; если же прошедшую дату всё-таки удаётся выбрать, при публикации сервер отклоняет заявку с сообщением об ошибке (дата загрузки не может быть раньше дня публикации).</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|validation</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-026</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Выбор типа ТС из чипов Transport (одиночный выбор)</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма «Yangi ariza yaratish»</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть чипы «Transport *»
-2. Тапнуть «Bortli 13.7»
-3. Тапнуть другой чип «Refrijerator 12.5»</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Доступны чипы: Bortli 13.7, Bortli 16, Bortli 17.5, Refrijerator 12.5, Baland bortli 13, Tentli 9.6. Выбор одиночный — при выборе нового чипа предыдущий снимается. Выбранный чип визуально выделен</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi ariza yaratish».</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть блок чипов «Transport *».
+2. Нажать чип «Bortli 13.7».
+3. Нажать другой чип — «Refrijerator 12.5».</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Доступны чипы: «Bortli 13.7», «Bortli 16», «Bortli 17.5», «Refrijerator 12.5», «Baland bortli 13», «Tentli 9.6». Выбор одиночный: при нажатии нового чипа выделение с предыдущего снимается. Выбранный чип визуально выделен.</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|validation</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-027</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Выбор количества водителей: 1 vs 2 haydovchi</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма «Yangi ariza yaratish»</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть «Haydovchilar soni *»
-2. Проверить значение по умолчанию
-3. Тапнуть «2 haydovchi»
-4. Вернуть «1 haydovchi»</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>По умолчанию выбрано «1 haydovchi». Переключение на «2 haydovchi» работает (одиночный выбор). Значения ограничены 1 и 2 (по API driversCount @Min(1)@Max(2))</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi ariza yaratish».</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть блок «Haydovchilar soni *» и значение по умолчанию.
+2. Нажать «2 haydovchi».
+3. Вернуть выбор на «1 haydovchi».</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>По умолчанию выбран «1 haydovchi» (1 водитель). Переключение на «2 haydovchi» и обратно работает, выбран всегда ровно один вариант. Других значений нет — число водителей может быть только 1 или 2.</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|boundary</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-028</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Предзаполнение маршрута сохранёнными складами</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Учётка с сохранёнными складами (напр. Nukus→Almata). Открыта форма</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть секцию «Yo'nalish *»
-2. Сверить предзаполненные точки</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Секция «Yo'nalish» предзаполнена дефолтными складами аккаунта: «откуда» (зелёная точка, город+склад) → «куда» (красная метка). Значения берутся из GET /locations/from и /locations/to (isDefault)</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Учётная запись с сохранёнными складами (например маршрут Nukus→Almata). Открыта форма «Yangi ariza yaratish».</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть секцию «Yo'nalish *».
+2. Сверить предзаполненные точки маршрута со складами учётной записи.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Секция «Yo'nalish» уже заполнена: точка «откуда» (зелёная точка, город и склад) и точка «куда» (красная метка) соответствуют складам, отмеченным у компании как склады по умолчанию.</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-029</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Валидация: обязательные поля не заполнены → «Ko'rib chiqish» не пускает дальше</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Свежая учётка без сохранённых складов ИЛИ снят тип ТС. Открыта форма</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>1. Не выбирать тип ТС и/или не задать маршрут
-2. Нажать «Ko'rib chiqish»</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Кнопка «Ko'rib chiqish» неактивна, пока не заполнены обязательные поля — дальше не пускает, пустую заявку создать нельзя. Проверено 2026-07-17: кнопка неактивна до заполнения.</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi ariza yaratish», обязательные поля не заполнены: учётная запись без сохранённых складов, либо снят выбор типа ТС.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. Оставить тип ТС и/или маршрут незаполненными.
+2. Попробовать нажать «Ko'rib chiqish».</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Кнопка «Ko'rib chiqish» неактивна, пока не заполнены все обязательные поля: перейти дальше и создать пустую заявку нельзя. Проверено 2026-07-17: кнопка неактивна до заполнения.</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|validation</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-030</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Поле комментариев Izohlar необязательное</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма «Yangi ariza yaratish»</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть поле «Izohlar» с плейсхолдером «Maxsus talablar...»
-2. Оставить пустым и пройти дальше
-3. На другом прогоне ввести текст комментария</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Поле «Izohlar» необязательное (без звёздочки): пустое не мешает публикации. Введённый текст сохраняется и уходит в notes (лимит 2000 символов на сервере)</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi ariza yaratish», обязательные поля заполнены.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть поле «Izohlar» с плейсхолдером «Maxsus talablar...» (особые требования).
+2. Оставить поле пустым и пройти дальше к просмотру и публикации.
+3. В отдельном прогоне создать заявку с введённым текстом комментария.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Поле «Izohlar» необязательное (без звёздочки): пустое значение публикации не мешает. Введённый комментарий сохраняется в заявке; максимальная длина комментария — 2000 символов (ограничение сервера).</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-031</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Создание заявки (Yangi ariza yaratish)</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Кнопка «Orqaga» возвращает без сохранения черновика</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма «Yangi ariza yaratish», часть полей заполнена</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>1. Заполнить тип ТС и число водителей
-2. Нажать «Orqaga» (или стрелку назад в шапке)</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>«Orqaga» возвращает без сохранения: повторный вход в создание заявки открывает чистую форму, черновик не хранится. Проверено 2026-07-17: форма чистая.</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi ariza yaratish», часть полей заполнена.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. Выбрать тип ТС и число водителей.
+2. Нажать «Orqaga» (или стрелку назад в шапке).
+3. Снова открыть создание заявки.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Возврат происходит без сохранения черновика: при повторном входе форма создания открывается чистой, ранее выбранные значения не восстанавливаются. Проверено 2026-07-17: форма чистая.</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-032</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Открытие списка адресов и добавление нового своего адреса</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Свежая учётка без сохранённых складов. В форме создания показаны плейсхолдеры «Yuklash manzili»/«Yetkazib berish manzili»</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть «Yuklash manzili»
-2. В шите тапнуть «O'z manzilingizni qo'shish»</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Открывается форма добавления адреса: выбор страны (Xitoy/Qirg'iziston), поиск города «Shaharni qidirish» и поле точного адреса «Ko'cha, uy, xonadon»</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Учётная запись без сохранённых складов. Открыта форма создания заявки: в секции маршрута показаны плейсхолдеры «Yuklash manzili» (адрес загрузки) и «Yetkazib berish manzili» (адрес доставки).</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Yuklash manzili».
+2. В открывшейся шторке нажать «O'z manzilingizni qo'shish» (добавить свой адрес).</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Открывается форма добавления адреса: выбор страны («Xitoy»/«Qirg'iziston»), поиск города «Shaharni qidirish» и поле точного адреса «Ko'cha, uy, xonadon» (улица, дом, помещение).</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-033</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Поиск города и сохранение адреса загрузки (Xitoy)</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма добавления адреса</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть страну «Xitoy»
-2. Тапнуть «Shaharni qidirish», ввести «Beijing»
-3. Дождаться результата «北京市 • bei jing» и выбрать его
-4. Тапнуть «Ko'cha, uy, xonadon», ввести «Loading street 1»
-5. Скрыть клавиатуру
-6. Нажать «Manzilni saqlash»</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Город найден поиском и выбран (передаётся реальный cityId). Адрес сохранён (POST /warehouse/locations → 201) и подставлен в точку «откуда» маршрута. Плейсхолдер «Yuklash manzili» заменён сохранённым адресом</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма добавления адреса (добавляется адрес загрузки).</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать страну «Xitoy».
+2. Нажать «Shaharni qidirish» и ввести «Beijing».
+3. Дождаться результата «北京市 • bei jing» и выбрать его.
+4. Нажать поле «Ko'cha, uy, xonadon» и ввести «Loading street 1».
+5. Скрыть клавиатуру и нажать «Manzilni saqlash» (сохранить адрес).</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Город находится поиском и выбирается именно из списка результатов (а не вводится вручную). Адрес сохраняется и подставляется в точку «откуда» маршрута: вместо плейсхолдера «Yuklash manzili» показан сохранённый адрес.</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-034</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Добавление адреса доставки (Yetkazib berish manzili)</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Адрес загрузки уже добавлен. Плейсхолдер «Yetkazib berish manzili» показан</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть «Yetkazib berish manzili»
-2. «O'z manzilingizni qo'shish» → «Xitoy»
-3. Поиск города «Beijing», выбрать «北京市 • bei jing»
-4. Ввести адрес «Delivery street 2»
-5. Нажать «Manzilni saqlash»</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Адрес доставки сохранён и подставлен в точку «куда» (красная метка). Маршрут «Yo'nalish» полностью заполнен (from→to), можно переходить к «Ko'rib chiqish»</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Адрес загрузки уже добавлен. В секции маршрута виден плейсхолдер «Yetkazib berish manzili».</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Yetkazib berish manzili».
+2. Нажать «O'z manzilingizni qo'shish» и выбрать страну «Xitoy».
+3. Найти город по запросу «Beijing» и выбрать «北京市 • bei jing».
+4. Ввести точный адрес «Delivery street 2».
+5. Нажать «Manzilni saqlash».</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Адрес доставки сохраняется и подставляется в точку «куда» маршрута (красная метка). Маршрут «Yo'nalish» полностью заполнен — и «откуда», и «куда», можно переходить к «Ko'rib chiqish».</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-035</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Валидация: сохранение без точного адреса</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма добавления адреса, выбран город</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>1. Выбрать страну и город
-2. Оставить «Ko'cha, uy, xonadon» пустым
-3. Нажать «Manzilni saqlash»</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Сохранение блокируется при пустом точном адресе: кнопка «Manzilni saqlash» неактивна. Проверено 2026-07-17: кнопка неактивна без адреса.</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма добавления адреса, страна и город выбраны.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. Оставить поле «Ko'cha, uy, xonadon» пустым.
+2. Посмотреть на кнопку «Manzilni saqlash» и попробовать её нажать.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Сохранить адрес без заполненного точного адреса нельзя: кнопка «Manzilni saqlash» неактивна. Проверено 2026-07-17: кнопка неактивна без адреса.</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|validation</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-036</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Выбор страны Qirg'iziston как альтернативы Xitoy</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма добавления адреса</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть выбор страны
-2. Выбрать «Qirg'iziston» (если доступна)
-3. Найти город и сохранить адрес</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Доступны страны Xitoy (CN) и Qirg'iziston (KG). Для KG поиск города и сохранение адреса работают аналогично Китаю. Проверено 2026-07-17: работает как для Китая.</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма добавления адреса.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть выбор страны.
+2. Выбрать «Qirg'iziston».
+3. Найти город поиском и сохранить адрес.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>В выборе доступны страны «Xitoy» (Китай) и «Qirg'iziston» (Кыргызстан). Для Кыргызстана поиск города и сохранение адреса работают так же, как для Китая. Проверено 2026-07-17: работает как для Китая.</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|validation</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-037</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Добавление адреса (Manzil qo'shish)</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Существующий сохранённый адрес выбирается из списка без повторного ввода</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Учётка с уже сохранёнными складами</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>1. В форме создания тапнуть точку маршрута (стрелку-редактирование)
-2. Выбрать сохранённый адрес из списка (без «O'z manzilingizni qo'shish»)</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Ранее сохранённые склады показаны списком, выбор подставляется в маршрут мгновенно (fromWarehouseId/toWarehouseId), без формы добавления. Блок добавления пропускается</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Учётная запись с уже сохранёнными складами. Открыта форма создания заявки.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. В секции маршрута нажать точку маршрута (стрелку редактирования).
+2. В открывшемся списке выбрать один из сохранённых адресов, не нажимая «O'z manzilingizni qo'shish».</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Ранее сохранённые склады показаны списком. Выбранный адрес сразу подставляется в маршрут — форма добавления нового адреса не открывается, повторный ввод города и улицы не требуется.</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-038</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Просмотр заявки (Ko'rib chiqish)</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Экран просмотра перед публикацией отображает введённые данные</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Форма заполнена (тип ТС, водители, маршрут from→to)</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>1. Нажать «Ko'rib chiqish»</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Открывается экран просмотра с итоговыми данными заявки: дата загрузки, тип ТС, число водителей, маршрут, комментарии. Присутствует кнопка «E'lon qilish» (публикация)</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Форма «Yangi ariza yaratish» заполнена: тип ТС, число водителей, маршрут «откуда → куда».</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Ko'rib chiqish».</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Открывается экран просмотра с итоговыми данными заявки: дата загрузки, тип ТС, число водителей, маршрут, комментарии — все значения совпадают с введёнными. Присутствует кнопка «E'lon qilish» (опубликовать).</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-039</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Просмотр заявки (Ko'rib chiqish)</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Публикация заявки: «E'lon qilish» → появление на вкладке «E'lon qilindi»</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран просмотра корректно заполненной заявки. loadDate=сегодня, без scheduledPublishDate</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>1. Нажать «E'lon qilish»
-2. Дождаться возврата к списку
-3. Открыть вкладку «E'lon qilindi»</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Заявка создаётся и публикуется немедленно (POST /orders → 201, status=PUBLISHED, currency=CNY по умолчанию, присвоен NAMA-xxxxx). Заявка видна на вкладке «E'lon qilindi», счётчик увеличился</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран просмотра корректно заполненной заявки. Дата загрузки — сегодня, отложенная публикация не задана.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «E'lon qilish».
+2. Дождаться возврата к списку заявок.
+3. Открыть вкладку «E'lon qilindi».</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Заявка создаётся и публикуется сразу: она появляется на вкладке «E'lon qilindi» с присвоенным номером вида «NAMA-…», счётчик вкладки увеличивается. Валюта новой заявки по умолчанию — юань (CNY).</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-040</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Просмотр заявки (Ko'rib chiqish)</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Защита от двойной публикации при повторных тапах «E'lon qilish»</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран просмотра заявки</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>1. Быстро дважды тапнуть «E'lon qilish»
-2. Проверить список на вкладке «E'lon qilindi»</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Создаётся ровно одна заявка. Кнопка должна блокироваться/показывать лоадер после первого тапа (без дубля POST /orders при быстром двойном тапе).</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран просмотра корректно заполненной заявки.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Быстро нажать «E'lon qilish» два раза подряд.
+2. Открыть вкладку «E'lon qilindi» и пересчитать новые заявки.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Создаётся ровно одна заявка — дубля в списке нет. После первого нажатия кнопка должна блокироваться или показывать индикатор загрузки, чтобы быстрый повторный тап не создал вторую такую же заявку.</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|network</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-042</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Секции деталей и статусная лента</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. Открыта заявка тапом с любой вкладки</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть детали заявки
-2. Осмотреть секции и статус</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Показаны секции заявки (маршрут, дата, тип ТС, число водителей, комментарии) и статусная лента, соответствующая вкладке. Внутренний «ID» может отличаться от отображаемого номера NAMA-xxxxx</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход. Детали заявки открыты нажатием на карточку с любой вкладки.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть детали заявки.
+2. Осмотреть секции и статус.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Показаны секции заявки (маршрут, дата, тип ТС, число водителей, комментарии) и статусная лента, соответствующая вкладке, с которой открыта заявка. Отображаемый номер имеет вид «NAMA-…»; внутренний идентификатор заявки может от него отличаться — это не дефект.</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-043</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Информация о водителе и госномере в IN_WORK</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Есть заявка «Ishda» (IN_WORK) с прикреплённым водителем</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть вкладку «Ishda»
-2. Открыть заявку с водителем
-3. Найти секцию «Haydovchi ma'lumotlari»</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Показана секция «Haydovchi ma'lumotlari» с ФИО водителя, строка «Davlat raqami» (госномер). Данные из GET /orders/{id} (drivers: name/phone/cardId/plate)</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Есть заявка на вкладке «Ishda» (в работе) с прикреплённым водителем.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть вкладку «Ishda».
+2. Открыть заявку с водителем.
+3. Найти секцию «Haydovchi ma'lumotlari» (данные водителя).</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>В деталях показана секция «Haydovchi ma'lumotlari»: ФИО водителя и строка «Davlat raqami» (госномер). Данные соответствуют водителю, назначенному на эту заявку (ФИО, телефон, госномер).</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-044</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Связь с водителем: диалог «Haydovchi bilan aloqa» доступен только в IN_WORK</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Заявка «Ishda» (IN_WORK)</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть заявку IN_WORK
-2. Тапнуть строку «Haydovchi bilan aloqa»
-3. Оценить диалог «Haydovchi bilan bog'landingizmi?»</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Открывается диалог с вариантами: «Tasdiqlandi» (CONFIRMED), «Rad etildi» (DECLINED), «Aloqasiz» (UNAVAILABLE), «Bog'lanish» (PENDING). Доступно только в IN_WORK (по API communication только IN_WORK, иначе 409 not-communicable)</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Есть заявка в статусе «Ishda» (в работе).</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть заявку со вкладки «Ishda».
+2. Нажать строку «Haydovchi bilan aloqa» (связь с водителем).
+3. Осмотреть диалог «Haydovchi bilan bog'landingizmi?» (связались ли вы с водителем).</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Открывается диалог с вариантами статуса связи: «Tasdiqlandi» (подтверждено), «Rad etildi» (отклонено), «Aloqasiz» (нет связи), «Bog'lanish» (связь ещё не состоялась). Установка статуса связи возможна только у заявок «Ishda» — в других статусах действие недоступно, сервер такие попытки отклоняет.</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-045</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Установка статуса связи «Tasdiqlandi» (CONFIRMED)</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Открыта заявка IN_WORK, открыт диалог связи</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>1. Выбрать «Tasdiqlandi»
-2. Вернуться к деталям</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Статус связи меняется на «Tasdiqlandi» (POST /communication → 204). Отображение в деталях обновляется. Это разблокирует отправку груза</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Открыта заявка «Ishda», открыт диалог «Haydovchi bilan aloqa».</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. Выбрать «Tasdiqlandi».
+2. Вернуться к деталям заявки.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Статус связи сохраняется: в деталях отображается «Tasdiqlandi». После этого становится доступной отправка груза (кнопка «Yuk jo'natildi»).</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-046</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Смена статуса связи на другие значения (Rad etildi/Aloqasiz)</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Открыта заявка IN_WORK</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть «Haydovchi bilan aloqa»
-2. Выбрать «Rad etildi»
-3. Повторно открыть и выбрать «Aloqasiz»</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Каждая смена принимается (204), статус связи перезаписывается (ортогональный суб-статус, заявка остаётся IN_WORK). UI отражает актуальный выбор</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Открыта заявка «Ishda».</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть «Haydovchi bilan aloqa» и выбрать «Rad etildi».
+2. Снова открыть диалог и выбрать «Aloqasiz».
+3. После каждого выбора проверять детали заявки.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Каждая смена статуса связи принимается и перезаписывает предыдущую — на экране всегда виден последний выбор. Основной статус заявки при этом не меняется: она остаётся в «Ishda».</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-047</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Отправка груза «Yuk jo'natildi» → «Yo'lda» (IN_TRANSIT)</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Заявка IN_WORK со статусом связи «Tasdiqlandi» (CONFIRMED)</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>1. Нажать «Yuk jo'natildi»
-2. В диалоге «Yuk jo'natilganini tasdiqlaysizmi?» подтвердить (тап «Yuk jo'natildi»)
-3. Проверить статус/вкладку</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>Груз отправлен (POST /goods-sent → 200), заявка переходит в «Yo'lda» (IN_TRANSIT). Появляется на вкладке «Yo'lda»</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Заявка в статусе «Ishda», статус связи с водителем — «Tasdiqlandi».</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1. В деталях заявки нажать «Yuk jo'natildi» (груз отправлен).
+2. В диалоге «Yuk jo'natilganini tasdiqlaysizmi?» (подтверждаете отправку груза?) нажать «Yuk jo'natildi».
+3. Вернуться к списку и проверить вкладки.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Отправка груза проходит успешно: заявка переходит в статус «Yo'lda» (в пути) — появляется на вкладке «Yo'lda» и исчезает со вкладки «Ishda».</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>mobile|positive|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-048</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Запрет отправки груза без подтверждения связи (не CONFIRMED)</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Заявка IN_WORK, статус связи НЕ «Tasdiqlandi» (напр. PENDING/DECLINED)</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть заявку IN_WORK без CONFIRMED
-2. Попытаться нажать «Yuk jo'natildi»</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Кнопка «Yuk jo'natildi» неактивна ИЛИ отправка отклоняется (сервер 409 error.order.not-ready-for-transit). Груз нельзя отправить, пока связь не «Tasdiqlandi»</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Заявка «Ishda», статус связи с водителем НЕ «Tasdiqlandi» (например, связь ещё не устанавливалась или выбран «Rad etildi»).</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть такую заявку.
+2. Попробовать нажать «Yuk jo'natildi».</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Отправить груз не удаётся: кнопка «Yuk jo'natildi» неактивна, либо отправка отклоняется с сообщением об ошибке. Пока связь с водителем не «Tasdiqlandi», перевести заявку в «Yo'lda» нельзя.</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-049</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Повторная отправка груза (идемпотентность)</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Заявка уже переведена в «Yo'lda» (IN_TRANSIT) после первого «Yuk jo'natildi»</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>1. Быстро дважды подтвердить в диалоге «Yuk jo'natildi»
-2. Либо открыть уже IN_TRANSIT заявку и снова попытаться отправить груз</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>goods-sent не идемпотентен (повтор на IN_TRANSIT → 409 error.order.not-ready-for-transit). UI должен блокировать кнопку после первого подтверждения и корректно обрабатывать 409, без ошибки/дубля.</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Заявка уже переведена в «Yo'lda» первой отправкой груза.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. В диалоге подтверждения быстро нажать «Yuk jo'natildi» два раза подряд.
+2. Либо открыть заявку, уже находящуюся в «Yo'lda», и попытаться отправить груз ещё раз.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Повторная отправка сервером отклоняется: заявка уже в пути, второй раз перевести её в «Yo'lda» нельзя. Приложение должно блокировать кнопку после первого подтверждения и спокойно обработать отказ — без сообщения о сбое и без дублей; заявка одна, статус остаётся «Yo'lda».</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|network|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-050</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Детали заявки (Ariza tafsilotlari)</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Связь и отправка груза недоступны вне IN_WORK</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Заявка в статусе PUBLISHED («E'lon qilindi») или IN_TRANSIT («Yo'lda»)</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть заявку не в IN_WORK
-2. Поискать строку «Haydovchi bilan aloqa» и кнопку «Yuk jo'natildi»</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Действия связи и отправки груза не показываются/недоступны вне IN_WORK. На PUBLISHED communication → 409 not-communicable, goods-sent → 409 not-ready. UI не должен предлагать эти действия</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Есть заявка в статусе «E'lon qilindi» (опубликована) или «Yo'lda» (в пути).</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть детали такой заявки.
+2. Поискать строку «Haydovchi bilan aloqa» и кнопку «Yuk jo'natildi».</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Вне статуса «Ishda» действия «связь с водителем» и «отправка груза» не показываются либо недоступны. Сервер такие действия в этих статусах тоже отклоняет, поэтому приложение не должно их предлагать.</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>mobile|negative|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-052</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Отображение ФИО и телефона профиля</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть «Profil» в нижней навигации
-2. Осмотреть шапку профиля</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Показан аватар с инициалами, ФИО (напр. «Бегимбаев Наврузбек Мамбетали») и телефон «+998900000004». Данные соответствуют вошедшему пользователю</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход сотрудником склада.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Profil» в нижней навигации.
+2. Осмотреть шапку профиля.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Показаны аватар с инициалами, ФИО (например «Бегимбаев Наврузбек Мамбетали») и телефон «+998900000004». Данные соответствуют пользователю, под которым выполнен вход.</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-053</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Пункт «Bildirishnomalar» (уведомления)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран профиля</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть карточку «Bildirishnomalar»</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Пункт «Bildirishnomalar»/«Уведомления» в профиле открывает экран уведомлений со списком (или пустым состоянием). Приложение не падает. Проверено 2026-07-17: открывается список уведомлений.</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран профиля.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать карточку «Bildirishnomalar» (уведомления).</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Открывается экран уведомлений: список уведомлений либо пустое состояние, если их нет. Приложение не падает. Проверено 2026-07-17: открывается список уведомлений.</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-055</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Выход «Chiqish» возвращает на экран входа</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран профиля</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть «Chiqish»
-2. Подтвердить выход, если запрошено</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>Сессия завершается, токен сбрасывается. Приложение возвращается на экран входа «Hisobingizga kiring». Повторный вход требует телефон+пароль. Список заявок недоступен без входа</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, открыт экран профиля.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Chiqish» (выход).
+2. Подтвердить выход, если появится запрос.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Сессия завершается: приложение возвращается на экран входа «Hisobingizga kiring», автоматического входа больше не происходит. Для повторного входа нужно заново ввести телефон и пароль; без входа список заявок недоступен.</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>mobile|session|positive</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-059</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Протухший/невалидный токен → релогин</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. Токен инвалидирован (истёк или отозван на бэке)</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>1. Оставить приложение и дождаться истечения токена (или отозвать сессию)
-2. Выполнить действие, требующее авторизации (открыть заявку/обновить список)</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>Сервер отвечает 401. Приложение выкидывает на экран входа для релогина (не показывает бесконечную ошибку). После входа доступ восстанавливается</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход. Сессия стала недействительной: истекла после длительного простоя либо отозвана на сервере.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Оставить приложение без активности до истечения сессии (или попросить отозвать сессию на сервере).
+2. Выполнить действие, требующее сервера: открыть заявку или обновить список.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Приложение переводит пользователя на экран входа для повторной авторизации — без бесконечной ошибки и без вечного индикатора загрузки. После повторного входа доступ к заявкам восстанавливается.</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>mobile|session|negative</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-060</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Фон/возврат приложения сохраняет сессию</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход, открыт список заявок</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>1. Свернуть приложение (Home)
-2. Открыть другое приложение
-3. Вернуться к приложению склада</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>Приложение восстанавливается на том же экране, сессия жива (без повторного входа при валидном токене). Список актуален или перезагружается</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, открыт список заявок.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Свернуть приложение кнопкой «Домой».
+2. Открыть любое другое приложение.
+3. Вернуться в приложение склада.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Приложение восстанавливается на том же экране, сессия сохраняется — повторный вход не требуется, пока она действительна. Список заявок актуален либо автоматически обновляется.</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>mobile|session|positive</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-062</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Повторные тапы по FAB не открывают несколько форм</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход, открыт список заявок</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>1. Быстро несколько раз тапнуть FAB «Ariza yaratish»</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Открывается ровно один bottom sheet «Transport turini tanlang». Множественные экраны/дубли не создаются</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, открыт список заявок.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Быстро нажать несколько раз подряд зелёную кнопку «+» (Ariza yaratish).</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Открывается ровно одна шторка «Transport turini tanlang». Несколько шторок или дублирующихся экранов не появляется.</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>MOB-WH-065</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Мобайл — Приложение склада</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Пустой список после выхода/входа другой учёткой (изоляция компаний)</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>Есть две учётки SHIPPER_WAREHOUSE разных компаний</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>1. Войти учёткой компании A, запомнить заявки
-2. Выйти («Chiqish»)
-3. Войти учёткой компании B</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Показаны только заявки компании B. Заявки компании A не видны (tenancy: список scoped по shipperCompanyId). Данные предыдущей сессии не утекают</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Есть две учётные записи сотрудников склада из разных компаний — A и B.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Войти учётной записью компании A и запомнить заявки в списке.
+2. Выйти: «Profil» → «Chiqish».
+3. Войти учётной записью компании B.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>После входа видны только заявки компании B. Заявки компании A нигде не отображаются: каждая компания видит только свои заявки, данные предыдущей сессии не остаются ни в списке, ни в профиле.</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>mobile|session|rbac</t>
         </is>
@@ -3241,3344 +3279,3355 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Happy path: вход TRANSPORT_ADMIN по телефону и паролю (200)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Установлено приложение перевозчика uz.logos.manzil.driver (clientType=TRANSPORT_COMPANY_APP), смотрит на staging-manzil.greatmall.uz. Есть учётка роли TRANSPORT_ADMIN (например +998900000002 / &lt;staging-password&gt;). Экран входа наблюдался вживую.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>1. Запустить приложение, дождаться экрана «Yana xush kelibsiz» (логотип «M Manzil», подзаголовок про грузы и маршруты).
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Установлено приложение перевозчика Manzil (Android), подключённое к стенду staging-manzil.greatmall.uz. Есть учётная запись транспортной компании (перевозчика) с известным паролем (например, телефон +998900000002).</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Запустить приложение и дождаться экрана входа «Yana xush kelibsiz» (логотип «M Manzil», подзаголовок про грузы и маршруты).
 2. В поле «Telefon raqam» (слева флаг и «+998 ⌄», плейсхолдер «00 000 00 00») ввести 9 цифр номера.
 3. В поле «Parol» ввести пароль.
 4. Убедиться, что кнопка «Kirish →» стала активной.
 5. Нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Вход выполнен (сервер 200 /auth/login + 200 /me). Открывается главный экран «Mavjud yuklar». Баннер ошибки не появляется.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Вход выполняется: открывается главный экран «Mavjud yuklar» (лента доступных грузов). Сообщение об ошибке не появляется.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Неверный пароль → 401 invalid-credentials</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Есть валидный телефон TRANSPORT_ADMIN. Экран входа наблюдался вживую.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Известен телефон действующей учётной записи транспортной компании. Открыт экран входа.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Ввести корректный телефон.
 2. Ввести заведомо неверный пароль.
 3. Нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Вход отклонён (сервер 401, code=error.invalid-credentials). Показывается сообщение об ошибке логина/пароля; пользователь остаётся на экране входа, поля сохранены.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Вход не выполняется: появляется сообщение об ошибке (неверный логин или пароль). Пользователь остаётся на экране входа, введённые значения полей сохраняются.</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Чужая роль SHIPPER_MANAGER в carrier-app → 403 wrong-app (ФАКТ, воспроизведено)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Учётка роли SHIPPER_MANAGER. Реально воспроизведено на staging под ТК-приложением.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести телефон менеджера-грузоотправителя.
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Есть учётная запись Менеджера грузоотправителя с верным паролем. Открыт экран входа приложения перевозчика.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести телефон менеджера грузоотправителя.
 2. Ввести его корректный пароль.
 3. Нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ФАКТ (воспроизведено): сервер возвращает 403 wrong-app. Вход в приложение перевозчика запрещён — гейт по clientType (в TRANSPORT_COMPANY_APP пускается только TRANSPORT_ADMIN). Пользователь остаётся на экране входа с сообщением об ошибке.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Вход не выполняется: в приложение перевозчика пускаются только учётные записи транспортных компаний, для чужой роли показывается сообщение об ошибке. Пользователь остаётся на экране входа (поведение воспроизведено на стенде).</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>mobile|rbac</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Роль SHIPPER_WAREHOUSE в carrier-app → 403 wrong-app</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Учётка склада SHIPPER_WAREHOUSE. Экран входа подтверждён вживую; фактический ответ по гейту clientType (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести телефон учётки склада.
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Есть учётная запись Сотрудника склада с верным паролем. Открыт экран входа приложения перевозчика.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести телефон учётной записи сотрудника склада.
 2. Ввести корректный пароль.
 3. Нажать «Kirish →».</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Вход отклонён гейтом clientType=TRANSPORT_COMPANY_APP (сервер 403 wrong-app), остаётся на экране входа. Проверено 2026-07-17: вход не выполнен; текст ошибки — generic «Непредвиденная ошибка. Попробуйте снова» вместо понятного wrong-app (→ BUG-029).</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Вход не выполняется — в приложение перевозчика чужая роль не допускается, пользователь остаётся на экране входа. Правильным считается понятное сообщение о том, что приложение не предназначено для этой учётной записи. Проверено 2026-07-17: вход не выполнен; текст ошибки — generic «Непредвиденная ошибка. Попробуйте снова» вместо понятного wrong-app (→ BUG-029).</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>mobile|rbac</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Кнопка «Kirish →» неактивна при пустых полях</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа. Наблюдалось вживую: кнопка неактивна при пустых полях.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть экран входа, ничего не вводить — проверить кнопку.
-2. Ввести только телефон, пароль оставить пустым — проверить кнопку.
-3. Ввести только пароль, телефон оставить пустым — проверить кнопку.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>На шагах 1–3 кнопка «Kirish →» неактивна (не синяя, не нажимается). Активируется только когда заполнены оба поля.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа, поля «Telefon raqam» и «Parol» пустые.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Ничего не вводя, посмотреть на кнопку «Kirish →».
+2. Ввести только телефон, пароль оставить пустым — снова посмотреть на кнопку.
+3. Очистить телефон и ввести только пароль — снова посмотреть на кнопку.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Во всех трёх случаях кнопка «Kirish →» неактивна (не подсвечена синим, нажатие не срабатывает). Кнопка становится активной только после заполнения обоих полей.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Показ/скрытие и очистка пароля</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа. В поле «Parol» справа наблюдались иконки крестик-очистка и глаз-показать.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа. В поле «Parol» справа есть две иконки: крестик (очистить) и глаз (показать пароль).</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Ввести пароль в поле «Parol».
-2. Нажать иконку глаза — пароль отображается открытым текстом.
-3. Нажать иконку глаза ещё раз — пароль снова маскируется точками.
-4. Нажать крестик-очистку.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Глаз переключает видимость пароля туда-обратно. Крестик полностью очищает поле пароля; после очистки кнопка «Kirish →» снова неактивна.</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+2. Нажать иконку глаза.
+3. Нажать иконку глаза ещё раз.
+4. Нажать иконку-крестик.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>После первого нажатия на глаз пароль показывается открытым текстом, после второго — снова маскируется точками. Крестик полностью очищает поле пароля; после очистки кнопка «Kirish →» снова неактивна.</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Телефон принимает ровно 9 цифр национального номера</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Открыт экран входа. Поле телефона: фиксированный флаг + «+998», плейсхолдер «00 000 00 00», 9 цифр.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>1. Начать вводить цифры в поле «Telefon raqam».
-2. Попробовать ввести буквы/символы.
-3. Ввести больше 9 цифр.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Префикс +998 фиксирован и не редактируется. Принимаются только цифры; ввод ограничен 9 цифрами (лишние не вводятся). Буквы/символы игнорируются.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран входа. Поле «Telefon raqam» с фиксированным флагом и кодом «+998», плейсхолдер «00 000 00 00».</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести цифры в поле «Telefon raqam».
+2. Попробовать ввести буквы и спецсимволы.
+3. Попробовать ввести больше 9 цифр.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Префикс +998 фиксирован и не редактируется. Поле принимает только цифры и не больше 9 — лишние цифры не появляются. Буквы и символы игнорируются.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-010</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Экран входа «Yana xush kelibsiz»</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Слишком много попыток входа → 429 (rate limit)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Есть валидный телефон. Настроен лимит попыток на сервере (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1. Несколько раз подряд быстро ввести неверный пароль и нажать «Kirish →».</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>После 5 неудачных попыток на телефон сервер отвечает 429; приложение показывает сообщение об ограничении. Проверено 2026-07-17: 429 срабатывает, но показан generic «Непредвиденная ошибка» вместо сообщения о лимите (→ BUG-029).</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Известен телефон действующей учётной записи перевозчика. Открыт экран входа. На сервере действует ограничение числа неудачных попыток входа.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Пять раз подряд ввести неверный пароль и нажать «Kirish →».
+2. Выполнить ещё одну попытку входа с этим же телефоном.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>После 5 неудачных попыток очередная попытка блокируется сервером; правильным считается понятное сообщение об ограничении числа попыток. Проверено 2026-07-17: 429 срабатывает, но показан generic «Непредвиденная ошибка» вместо сообщения о лимите (→ BUG-029).</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>mobile|network</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-013</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Happy path: отображение ленты доступных грузов</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход как TRANSPORT_ADMIN. Экран «Mavjud yuklar» подтверждён вживую (вкладка Buyurtmalar активна).</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>1. После входа дождаться загрузки вкладки «Buyurtmalar».
-2. Осмотреть заголовок «Mavjud yuklar» и список карточек грузов.
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход как транспортная компания (перевозчик).</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Дождаться загрузки нижней вкладки «Buyurtmalar».
+2. Осмотреть заголовок «Mavjud yuklar», строку поиска и список карточек грузов.
 3. Осмотреть нижнюю навигацию.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Показан заголовок «Mavjud yuklar», строка поиска и список карточек (PUBLISHED/QUOTED из обслуживаемых городов, sort по дате создания desc). Нижняя навигация: «Buyurtmalar» (активна), «Takliflar», «Profil». Грузы, по которым компания уже бидила, в ленте отсутствуют (живут во вкладке Takliflar).</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Показаны заголовок «Mavjud yuklar», строка поиска и список карточек грузов. В ленте — опубликованные заявки, открытые для предложений, из городов, которые обслуживает компания; новые сверху. Заявок, по которым компания уже отправила предложение, в ленте нет — они показываются во вкладке «Takliflar». Нижняя навигация: «Buyurtmalar» (активна), «Takliflar», «Profil».</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-014</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Состав карточки груза: номер, маршрут, дата, тип ТС, бейдж Avto</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>В ленте есть хотя бы один груз. Наблюдалось вживую.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, в ленте «Mavjud yuklar» есть хотя бы один груз.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Рассмотреть карточку груза в ленте.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>На карточке: слева синяя точка + номер груза (наблюдались разные префиксы: NAMA-00011, UEIE-00026/25/24), справа бейдж типа транспорта «Avto». Строка маршрута «город отправления → город назначения». Внизу дата загрузки (2026-07-15) и иконка ТС с типом.</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>На карточке: слева синяя точка и номер груза (встречались разные серии номеров: NAMA-00011, UEIE-00026/25/24), справа бейдж типа транспорта «Avto». Ниже строка маршрута «город отправления → город назначения». Внизу дата загрузки (2026-07-15) и иконка транспорта с типом ТС.</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-016</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Поиск по маршруту / ТК / ID</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>В ленте несколько грузов. Поле поиска «Marshrut, TC, ID bo'yicha qidirish...» подтверждено вживую.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>1. В строке поиска ввести часть номера груза (например «00011»).
-2. Очистить, ввести название города маршрута.
-3. Очистить, ввести несуществующую строку.</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Лента фильтруется по совпадению (search матчит номер заказа и notes). По городу — грузы соответствующего маршрута. По несуществующей строке — пустой результат/пустое состояние. Очистка поиска возвращает полную ленту.</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, в ленте «Mavjud yuklar» несколько грузов. Вверху строка поиска «Marshrut, TC, ID bo'yicha qidirish...».</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести в поиск часть номера груза (например «00011»).
+2. Очистить поиск и ввести название города из маршрута.
+3. Очистить поиск и ввести заведомо несуществующую строку.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Лента фильтруется: по части номера остаются только совпадающие грузы (поиск ищет по номеру заявки и примечанию к ней), по городу — грузы соответствующего маршрута, по несуществующей строке — пустой результат (пустое состояние). После очистки поиска возвращается полная лента.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-017</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Фильтрация ленты по обслуживаемым городам компании</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>У компании ограниченный список обслуживаемых городов (isAll=false). Серверный гейт fromOrToWarehouseIn.</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>1. Просмотреть ленту грузов.
-2. Сверить города отправления/назначения карточек с обслуживаемыми компанией.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>В ленте видны только грузы, где origin ИЛИ destination входит в обслуживаемые города компании. Грузы полностью вне обслуживаемых городов не показываются.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход под компанией с ограниченным списком обслуживаемых городов (не «все города»); список известен (настраивается в веб-кабинете администратора).</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Просмотреть ленту «Mavjud yuklar».
+2. Сверить города отправления и назначения на карточках со списком обслуживаемых городов компании.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>В ленте видны только грузы, у которых город отправления ИЛИ город назначения входит в список обслуживаемых городов компании. Грузы, у которых оба города вне списка, не показываются.</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-018</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Компания обслуживает все города (isAll=true) — видит любой город</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>У компании isAll=true (обслуживает все города).</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>1. Просмотреть ленту грузов.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Показаны PUBLISHED/QUOTED-грузы всех городов (гейт по обслуживаемым городам снят). Прочие фильтры (уже бидили, ЧС складов, исключение) продолжают действовать.</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход под компанией, настроенной на обслуживание всех городов.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Просмотреть ленту «Mavjud yuklar».</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>В ленте показываются открытые для предложений заявки из любых городов — ограничение по обслуживаемым городам не действует. Остальные правила скрытия продолжают работать: не показываются заявки, по которым уже отправлено предложение, заявки со складами из чёрного списка компании и заявки, где компания исключена после перевыпуска тендера.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-019</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Груз со складом из ЧС компании скрыт из ленты</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>У компании есть склады в чёрном списке (blacklistWarehouseIds). Серверный гейт fromAndToWarehouseNotIn.</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>1. Просмотреть ленту грузов.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Грузы, у которых склад отправления ИЛИ назначения в ЧС компании, в ленте отсутствуют.</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход под компанией, у которой есть склады в чёрном списке; известно, какие заявки идут с этих складов или на них.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Просмотреть ленту «Mavjud yuklar».
+2. Поискать заявки, затрагивающие склады из чёрного списка компании.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Заявки, у которых склад отправления ИЛИ склад назначения находится в чёрном списке компании, в ленте отсутствуют.</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-020</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Компания исключена как бывший победитель — груз скрыт</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Заказ перевыпущен (CHANGED/REVERT), компания попала в excludedTransportCompanyId.</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>1. Просмотреть ленту грузов.</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Перевыпущенный груз скрыт от исключённого перевозчика (notExcludedForTransportCompany). При попытке подать оффер на такой груз сервер вернёт carrier-excluded.</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>По заявке ранее был выбран победитель — эта компания; затем тендер перевыпущен (заявка снова опубликована), и компания исключена из повторного тендера. Выполнен вход под этой компанией.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Просмотреть ленту «Mavjud yuklar».
+2. Поискать перевыпущенную заявку.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Перевыпущенная заявка скрыта от исключённой компании — в ленте её нет. Если попытаться отправить предложение по ней обходным путём, сервер отклонит его с ошибкой о том, что перевозчик исключён по данной заявке.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-021</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Пустое состояние ленты (нет доступных грузов)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Учётка, для которой нет ни одного PUBLISHED/QUOTED-груза в обслуживаемых городах.</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Учётная запись перевозчика, для которой сейчас нет ни одной доступной заявки (в обслуживаемых городах ничего не опубликовано).</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Открыть вкладку «Buyurtmalar».</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>После скелетонов загрузки показывается пустое состояние (нет карточек грузов), без бесконечного спиннера и без краша.</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>После плашек-заглушек (скелетонов) загрузки показывается пустое состояние — карточек грузов нет. Бесконечный спиннер не висит, приложение не падает.</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-022</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Прокрутка и пагинация ленты</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>В ленте больше 20 грузов (страница по умолчанию size=20).</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>1. Прокрутить ленту вниз до конца первой страницы.
-2. Продолжить прокрутку.</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Подгружается следующая страница грузов (бесконечная прокрутка/пагинация), сортировка по дате создания desc сохраняется, дубликатов карточек нет.</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, в ленте больше 20 грузов (за один раз лента загружает 20 карточек).</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Прокрутить ленту вниз до конца первых 20 карточек.
+2. Продолжить прокрутку вниз.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Следующая порция грузов подгружается автоматически (бесконечная прокрутка). Порядок «новые сверху» сохраняется, дубликатов карточек нет.</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-024</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Лента «Mavjud yuklar»</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Открытие деталей груза по тапу на карточку</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>В ленте есть груз. Переход подтверждён вживую.</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть по карточке груза.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Открывается экран «Yuk tafsilotlari» выбранного груза (номер в шапке совпадает с карточкой).</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, в ленте «Mavjud yuklar» есть груз.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать на карточку груза.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Открывается экран деталей «Yuk tafsilotlari» выбранного груза; номер груза в шапке совпадает с номером на карточке.</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-025</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Детали груза «Yuk tafsilotlari»</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Happy path: состав экрана деталей</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Открыт груз из ленты. Экран подтверждён вживую.</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть шапку (номер груза, «Yuk tafsilotlari», колокольчик, стрелка назад).
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран «Yuk tafsilotlari» груза из ленты.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть шапку экрана.
 2. Осмотреть карточку маршрута.
 3. Осмотреть секцию «Yuk spetsifikatsiyasi».
-4. Осмотреть кнопку внизу.</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Показаны: шапка с номером (напр. NAMA-00011), карточка маршрута откуда→куда, секция спецификации со строками Transport (тип ТС), «Haydovchilar soni» (число водителей, напр. 1), «Uzunlik» (длина, 13.7 m), «Yuklash sanasi» (2026-07-15), «To'lov turi» (CNY). Внизу кнопка «Taklif yuborish».</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
+4. Прокрутить вниз и осмотреть кнопку внизу экрана.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>В шапке: стрелка назад, номер груза (напр. NAMA-00011), заголовок «Yuk tafsilotlari» и колокольчик уведомлений. Ниже — карточка маршрута «откуда → куда». В секции спецификации строки: «Transport» (тип ТС), «Haydovchilar soni» (число водителей, напр. 1), «Uzunlik» (длина, 13.7 m), «Yuklash sanasi» (2026-07-15), «To'lov turi» (CNY). Внизу — кнопка «Taklif yuborish».</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-027</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Детали груза «Yuk tafsilotlari»</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Тип оплаты в CNY по умолчанию</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Открыт груз. Наблюдалось вживую: «To'lov turi» = CNY.</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>1. Посмотреть строку «To'lov turi» в спецификации.</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Тип оплаты/валюта отображается как CNY (валюта наследуется от заказа). Далее в форме оффера поле цены будет с префиксом ¥ (CNY).</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран «Yuk tafsilotlari» груза.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. Найти в секции спецификации строку «To'lov turi».
+2. Нажать «Taklif yuborish» и посмотреть на поле цены.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>В строке «To'lov turi» указана валюта CNY (валюта наследуется от заявки). На форме предложения поле цены отображается с префиксом ¥ (CNY).</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-028</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Детали груза «Yuk tafsilotlari»</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Кнопка «Taklif yuborish» ведёт на форму оффера</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Открыт груз PUBLISHED/QUOTED, по которому компания ещё не бидила.</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>1. Нажать «Taklif yuborish» внизу деталей.</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Открывается форма оффера «Taklif yuborish» с номером того же груза и карточкой маршрута.</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран «Yuk tafsilotlari» заявки, открытой для предложений; компания по ней предложение ещё не подавала.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать кнопку «Taklif yuborish» внизу экрана.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Открывается форма «Taklif yuborish» с номером того же груза и карточкой маршрута.</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-031</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Happy path: подача оффера с ценой (201, груз PUBLISHED→QUOTED на первом биде)</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Груз PUBLISHED/QUOTED в scope, компания ещё не бидила и не исключена. Форма подтверждена вживую до конца подача не прокликана (проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>1. На форме «Taklif yuborish» в поле «Sizning taklifingiz» (префикс ¥) ввести цену числовой клавиатурой.
-2. При необходимости заполнить «Dispetcher uchun izoh».
-3. Убедиться, что «Yuborish» стала активной.
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Заявка открыта для предложений и видна в ленте компании; компания по ней ещё не подавала предложение и не исключена. Открыта форма «Taklif yuborish» этой заявки.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. В поле «Sizning taklifingiz» (префикс ¥) ввести цену с числовой клавиатуры.
+2. При желании заполнить комментарий «Dispetcher uchun izoh».
+3. Убедиться, что кнопка «Yuborish» стала активной.
 4. Нажать «Yuborish».</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Предложение цены отправлено (сервер 201), показано подтверждение, оффер в статусе PENDING, цена сохранена. Проверено 2026-07-17: подача оффера работает.</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Предложение отправляется без ошибок, показывается подтверждение. Предложение появляется во вкладке «Takliflar» как новое (на рассмотрении), введённая цена сохранена. Проверено 2026-07-17: подача оффера работает.</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-032</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Кнопка «Yuborish» неактивна без цены</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма оффера. Наблюдалось вживую: «Yuborish» неактивна, пока не введена цена.</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Taklif yuborish», поле цены пустое.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Оставить поле цены «Sizning taklifingiz» пустым.
 2. Заполнить только комментарий «Dispetcher uchun izoh».
-3. Проверить кнопку «Yuborish».</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Кнопка «Yuborish» остаётся неактивной, пока не введена цена. Комментарий сам по себе не активирует отправку.</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
+3. Посмотреть на кнопку «Yuborish».</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Кнопка «Yuborish» остаётся неактивной, пока не введена цена. Заполненный комментарий сам по себе отправку не активирует.</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-033</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Валидация цены: 0 отклоняется</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма оффера. Сервер: @Positive на price.</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Taklif yuborish».</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. В поле цены ввести 0.
-2. Попытаться отправить оффер.</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Отправка отклоняется (клиентская валидация «цена &gt; 0» или сервер 400 @Positive по полю price). Показывается сообщение о некорректной цене; оффер не создаётся.</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
+2. Попытаться отправить предложение кнопкой «Yuborish».</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Предложение с нулевой ценой не создаётся: либо приложение не даёт отправить (цена должна быть больше нуля), либо после отправки показывается сообщение о некорректной цене.</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-034</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Валидация цены: отрицательное значение отклоняется</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма оффера. Сервер: @Positive.</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>1. Попытаться ввести отрицательную цену (например -100).
-2. Отправить оффер.</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Числовая клавиатура с префиксом ¥ не даёт ввести минус, либо отправка блокируется/сервер 400 @Positive. Оффер не создаётся.</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Taklif yuborish».</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. Попробовать ввести в поле цены отрицательное значение (например -100).
+2. Если минус ввести удалось — нажать «Yuborish».</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Числовая клавиатура поля цены (с префиксом ¥) не даёт ввести минус; если отрицательное значение всё же оказалось в поле, отправка блокируется или показывается сообщение об ошибке. Предложение с отрицательной ценой не создаётся.</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-035</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Валидация цены: нечисловой ввод/буквы не проходят</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма оффера. Поле цены с числовой клавиатурой.</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>1. Попытаться ввести буквы/несколько разделителей/пробелы в поле цены.</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Поле принимает только корректное число (числовая клавиатура). Буквы и лишние разделители не вводятся; форма не отправляется с невалидным значением.</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Taklif yuborish», у поля цены числовая клавиатура.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. Попробовать ввести в поле цены буквы.
+2. Попробовать ввести несколько разделителей (точек/запятых) подряд и пробелы.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Поле принимает только корректное число: буквы, пробелы и лишние разделители не вводятся. Отправить форму с невалидным значением цены невозможно.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-036</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Очень большая цена при PATCH-редактировании оффера</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Оффер уже подан (PENDING), выполняется редактирование. При PATCH-редактировании верхняя граница цены обрабатывается сервером как 409 (не 500).</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть редактирование своего PENDING-оффера.
-2. Ввести цену выше NUMERIC(15,2), напр. 10000000000000.00.
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Компания уже подала предложение по заявке, оно ещё на рассмотрении и доступно для редактирования.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. Во вкладке «Takliflar» открыть своё предложение и перейти к редактированию.
+2. Ввести заведомо слишком большую цену, например 10000000000000.00.
 3. Сохранить.</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Очень большая цена при редактировании оффера обрабатывается сервером как 409 Conflict (не 500). Приложение должно корректно показать ошибку, не крашась. (Проверено на backend: 1e15 → 409.)</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение не проходит: сервер отвечает контролируемой ошибкой-конфликтом, а не внутренней ошибкой. Приложение показывает сообщение об ошибке и не падает. (Проверено на backend: 1e15 → 409.)</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-037</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Дата загрузки readonly, комментарий необязателен</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма оффера. Наблюдалось вживую.</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>1. Попытаться изменить поле «Yuklash sanasi».
-2. Оставить «Dispetcher uchun izoh» пустым и отправить оффер с введённой ценой.</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Поле «Yuklash sanasi» серое/readonly (2026-07-15), не редактируется. Комментарий «Dispetcher uchun izoh» необязателен — оффер отправляется без него.</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Taklif yuborish».</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. Попробовать изменить значение поля «Yuklash sanasi».
+2. Ввести цену, поле «Dispetcher uchun izoh» оставить пустым.
+3. Нажать «Yuborish».</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Поле «Yuklash sanasi» серое, только для чтения (2026-07-15) — изменить его нельзя. Комментарий необязателен: предложение только с ценой отправляется успешно.</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-038</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Кнопка «Bekor qilish» отменяет подачу</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма оффера, введена цена. Наблюдалось вживую.</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Taklif yuborish», в поле цены введено значение.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Bekor qilish».</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Форма закрывается, предложение не создаётся; происходит возврат на экран деталей груза. Груз остаётся в ленте «Mavjud yuklar».</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>mobile|positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>MOB-CR-039</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Форма оффера «Taklif yuborish»</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Повторная подача той же компанией → already-submitted</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>У компании уже есть активное предложение по грузу (по одной заявке от компании допускается только одно предложение). Форма подачи по этому грузу открыта повторно — например, на втором устройстве под той же компанией или на устаревшем, заранее открытом экране.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Ввести цену.
-2. Нажать «Bekor qilish».</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Форма закрывается без создания оффера; возврат к деталям груза. Груз остаётся в ленте (оффер не подан).</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
+2. Нажать «Yuborish».</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Второе предложение не создаётся: показывается сообщение, что предложение по этой заявке уже отправлено. В норме такой груз уже не отображается в ленте «Mavjud yuklar» — он виден во вкладке «Takliflar».</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>mobile|negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>MOB-CR-040</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Форма оффера «Taklif yuborish»</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Груз больше не открыт для бидов → not-open-for-bids</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Форма предложения открыта заранее по заявке, которая тем временем закрылась для предложений (диспетчер выбрал победителя или заявка отменена).</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести цену.
+2. Нажать «Yuborish».
+3. Вернуться в ленту «Mavjud yuklar» и поискать эту заявку.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Заявка с выбранным победителем пропадает из ленты доступных у других перевозчиков — подать по ней предложение через приложение нельзя (она не видна). Отправку с заранее открытой формы сервер отклоняет с сообщением, что приём предложений по заявке закрыт. Проверено 2026-07-17: заявка исчезает из списка у других.</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>mobile|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>MOB-CR-041</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Форма оффера «Taklif yuborish»</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Исключённый перевозчик подаёт оффер → carrier-excluded</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Тендер по заявке перевыпущен, компания (бывший победитель) исключена из повторного тендера. Выполнен вход под этой компанией.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Поискать перевыпущенную заявку в ленте «Mavjud yuklar».
+2. Если форма предложения по этой заявке осталась открытой — ввести цену и нажать «Yuborish».</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Заявка скрыта из ленты исключённой компании; подать предложение через приложение нельзя. Попытка отправить предложение обходным путём отклоняется сервером с ошибкой об исключённом перевозчике. Проверено 2026-07-17: заказ NAMA-00019 отсутствует в ленте исключённого перевозчика (UI) + 409 по API.</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>mobile|positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>MOB-CR-039</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>mobile|lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>MOB-CR-042</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Форма оффера «Taklif yuborish»</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Повторная подача той же компанией → already-submitted</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>У компании уже есть активный оффер на этот груз (пара заказ+ТК уникальна).</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>1. Попытаться подать второй оффер на тот же груз (например через устаревшую карточку/deeplink).
-2. Ввести цену и нажать «Yuborish».</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Сервер 409, code=error.offer.already-submitted. Приложение показывает, что предложение уже отправлено; второй оффер не создаётся. В норме груз уже не должен быть в ленте (он во вкладке Takliflar).</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование оффера доступно только в статусе PENDING</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>У компании есть предложения в разных состояниях: на рассмотрении, принятое (тендер выигран) и отклонённое.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть предложение, которое ещё на рассмотрении, изменить цену или комментарий и сохранить.
+2. Открыть принятое или отклонённое предложение и попытаться его изменить.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Пока предложение на рассмотрении, оно редактируется — новая цена сохраняется. Принятое или отклонённое предложение изменить нельзя: редактирование недоступно. Проверено 2026-07-17: изменение цены в PENDING сохраняется.</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>mobile|negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>MOB-CR-040</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Форма оффера «Taklif yuborish»</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Груз больше не открыт для бидов → not-open-for-bids</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Груз к моменту отправки перешёл в статус вне PUBLISHED/QUOTED (SELECTED/IN_WORK/CANCELLED и т.п.).</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть форму оффера по грузу, который тем временем закрылся для бидов.
-2. Ввести цену и нажать «Yuborish».</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Заявка с выбранным победителем пропадает из ленты доступных у других перевозчиков — подать по ней оффер через UI нельзя (не видна). Ошибка not-open-for-bids — backend-подстраховка (при обращении по id). Проверено 2026-07-17: заявка исчезает из списка у других.</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>MOB-CR-041</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Форма оффера «Taklif yuborish»</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Исключённый перевозчик подаёт оффер → carrier-excluded</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Компания исключена по этому заказу (excludedTransportCompanyId после перевыпуска тендера).</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>1. Попытаться подать оффер на перевыпущенный груз, где компания исключена.
-2. Нажать «Yuborish».</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Компания исключена по заказу (excludedTransportCompanyId после перевыпуска тендера): заказ скрыт из ленты перевозчика; прямой ре-бид → 409 error.offer.carrier-excluded. Проверено 2026-07-17: заказ NAMA-00019 отсутствует в ленте исключённого перевозчика (UI) + 409 по API.</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>mobile|lifecycle</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>MOB-CR-042</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Форма оффера «Taklif yuborish»</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Редактирование оффера доступно только в статусе PENDING</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>У компании есть офферы в разных статусах (PENDING / SELECTED / REJECTED).</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть оффер в статусе PENDING → изменить цену/комментарий → сохранить.
-2. Открыть оффер в статусе SELECTED или REJECTED → попытаться изменить.</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Пока предложение в статусе PENDING — его можно отредактировать (новая цена сохраняется); в других статусах редактирование недоступно. Проверено 2026-07-17: изменение цены в PENDING сохраняется.</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>mobile|lifecycle</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-043</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Happy path: вкладки статусов со счётчиками</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. Вкладка «Takliflar» подтверждена вживую (у тест-аккаунта: Yangi 0, Tanlangan 0, Jarayonda 4).</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход как транспортная компания. У тестового аккаунта наблюдались счётчики: Yangi 0, Tanlangan 0, Jarayonda 4.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Перейти на нижнюю вкладку «Takliflar».
 2. Осмотреть горизонтальные вкладки статусов и их счётчики.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Показаны горизонтально прокручиваемые вкладки: «Yangi» (новые), «Tanlangan» (выбранные), «Jarayonda» (в процессе), «Yo'lda» (в пути) — каждая со счётчиком. Значения соответствуют per-status сводке (feed/summary won-карта).</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Показаны горизонтально прокручиваемые вкладки со счётчиками: «Yangi» (новые), «Tanlangan» (выбранные), «Jarayonda» (в процессе), «Yo'lda» (в пути). Счётчик каждой вкладки соответствует фактическому количеству предложений/заявок в этом состоянии.</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-044</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Скелетоны загрузки сменяются контентом</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Открыта вкладка «Takliflar». Наблюдалось вживую: сначала скелетоны, затем контент/пустое состояние.</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть/обновить вкладку «Takliflar».
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, доступна вкладка «Takliflar».</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть (или обновить) вкладку «Takliflar».
 2. Понаблюдать за загрузкой.</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Сначала показываются скелетоны загрузки, затем — либо список офферов, либо пустое состояние. Нет зависания на скелетонах.</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Сначала показываются плашки-заглушки (скелетоны) загрузки, затем они сменяются списком предложений либо пустым состоянием. Зависания на скелетонах нет.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-045</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Пустое состояние «Faol takliflar yo'q» (вкладка Yangi)</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Нет активных офферов в статусе Yangi. Подтверждено вживую.</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть вкладку «Takliflar», выбрать статус «Yangi» (счётчик 0).</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Показана карточка с пунктирной рамкой и иконкой-конвертом, текст «Faol takliflar yo'q» и подсказка «Yukni oching va taklif yuboring — bu yerda paydo bo'ladi».</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход; на вкладке статуса «Yangi» нет активных предложений (счётчик 0).</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть вкладку «Takliflar».
+2. Выбрать вкладку статуса «Yangi».</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Показана карточка с пунктирной рамкой и иконкой-конвертом: текст «Faol takliflar yo'q» и подсказка «Yukni oching va taklif yuboring — bu yerda paydo bo'ladi».</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-046</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Переключение между вкладками статусов</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Открыта вкладка «Takliflar», у аккаунта есть офферы в Jarayonda.</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>1. Переключиться Yangi → Tanlangan → Jarayonda → Yo'lda.
-2. На каждой вкладке осмотреть содержимое.</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Список фильтруется по выбранному статусу связанного заказа; счётчик вкладки совпадает с числом карточек. Jarayonda показывает выигранные грузы в работе (у тест-аккаунта 4).</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Открыта вкладка «Takliflar»; у аккаунта есть заявки в состоянии «Jarayonda» (у тестового аккаунта — 4).</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1. Переключаться по вкладкам: «Yangi» → «Tanlangan» → «Jarayonda» → «Yo'lda».
+2. На каждой вкладке осмотреть содержимое списка.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>На каждой вкладке список фильтруется по соответствующему состоянию заявки; количество карточек совпадает со счётчиком вкладки. «Jarayonda» показывает выигранные грузы в работе (у тестового аккаунта 4).</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-047</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Карточка оффера открывает детали выигранного/поданного груза</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>На вкладке есть офферы. Детали остаются доступны даже вне PUBLISHED/QUOTED (bid != null).</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть по карточке оффера (например в Jarayonda).</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Открываются детали груза с заполненными полями активного бида (сумма/комментарий). Для выигранного груза (Tanlangan/Jarayonda) доступны действия по водителям.</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Во вкладке «Takliflar» есть предложения (например в «Jarayonda»). Детали груза по поданному предложению остаются доступны и после закрытия тендера.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать на карточку предложения (например во вкладке «Jarayonda»).</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Открываются детали груза, в них видны данные поданного предложения: сумма и комментарий. Для выигранного груза (вкладки «Tanlangan»/«Jarayonda») доступны действия с водителями.</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-048</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Назначение водителя на выигранный груз (Tanlangan/Jarayonda)</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Есть выигранный груз в статусе SELECTED (Tanlangan). Водитель свободен, с cardId, той же компании. Проверить на устройстве (ветка не прокликана до конца).</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть выигранный груз во вкладке Tanlangan.
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Компания выиграла тендер: груз находится во вкладке «Tanlangan». В автопарке есть свободный водитель этой компании с заполненным номером ID-карты.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть выигранный груз во вкладке «Tanlangan».
 2. Перейти к назначению водителей.
-3. Выбрать свободного водителя из списка и указать госномер (licensePlate).
+3. Выбрать свободного водителя из списка и указать госномер транспортного средства.
 4. Сохранить назначение.</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Водитель прикрепляется к выигранному грузу (сохраняется без ошибки), виден на карточке груза. Проверено 2026-07-17: назначение водителя работает.</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Назначение сохраняется без ошибок; водитель отображается прикреплённым к грузу. Проверено 2026-07-17: назначение водителя работает.</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-049</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Старт работы по грузу (SELECTED→IN_WORK) при полном комплекте водителей</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Выигранный груз SELECTED, прикреплено &gt;= driversCount водителей. Проверить на устройстве.</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть выигранный груз с назначенными водителями.
-2. Нажать кнопку старта работы.</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>При полном комплекте водителей груз переходит SELECTED→IN_WORK (старт работает). Проверено 2026-07-20: назначение всех водителей и старт работают. Примечание: при НЕполном комплекте (1 из 2) приложение показывает вводящее в заблуждение сообщение (→ BUG-030), но функционально всё ок.</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Выигранный груз во вкладке «Tanlangan»; назначено столько водителей, сколько требуется по заявке (строка «Haydovchilar soni»).</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть выигранный груз с полным комплектом назначенных водителей.
+2. Нажать кнопку старта работы по грузу.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Старт проходит: заявка переходит в работу, карточка перемещается из «Tanlangan» в «Jarayonda». Проверено 2026-07-20: назначение всех водителей и старт работают. Примечание: при НЕполном комплекте (1 из 2) приложение показывает вводящее в заблуждение сообщение (→ BUG-030), но функционально всё ок.</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-050</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Замена/отцепление водителя на выигранном грузе</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Выигранный груз SELECTED/IN_WORK с назначенным водителем. Проверить на устройстве.</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Выигранный груз (во вкладке «Tanlangan» или «Jarayonda») с назначенным водителем; в автопарке есть другой свободный водитель.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Открыть выигранный груз.
-2. Заменить назначенного водителя на другого свободного (или отцепить).</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>Замена/отцепление водителя на выигранном грузе работает: новый водитель встаёт на место (в SELECTED можно до нуля; в IN_WORK нельзя убрать последнего). Проверено 2026-07-20: замена функционально работает. Примечания: неверный текст ошибки (→ BUG-030) и уже-назначенный водитель в списке кандидатов (→ BUG-031).</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
+2. Заменить назначенного водителя на другого свободного (или открепить его).</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Замена работает: новый водитель занимает место прежнего. Пока работа не начата (груз в «Tanlangan»), водителей можно снимать вплоть до нуля; после старта (груз в «Jarayonda») последнего водителя снять нельзя. Проверено 2026-07-20: замена функционально работает. Примечания: неверный текст ошибки (→ BUG-030) и уже-назначенный водитель в списке кандидатов (→ BUG-031).</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-051</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Takliflar»</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Список офферов отсортирован новыми сверху; офферы удалённых грузов скрыты</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>У компании несколько офферов, часть по удалённым заказам.</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>У компании несколько предложений; часть из них — по заявкам, которые после подачи были удалены (удаление выполняется в веб-кабинете грузоотправителя).</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Открыть вкладку «Takliflar».
-2. Оценить порядок карточек и отсутствие «мёртвых» грузов.</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Офферы отсортированы по дате создания desc (новые первыми). Офферы по удалённым/неживым заказам не показываются (orderLive-фильтр).</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
+2. Оценить порядок карточек в списке.
+3. Поискать предложения по удалённым заявкам.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Предложения отсортированы новыми сверху (по дате создания). Предложений по удалённым заявкам в списке нет.</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-052</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Happy path: шапка профиля ТК</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Выполнен вход. Экран профиля подтверждён вживую.</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>1. Перейти на вкладку «Profil».
-2. Осмотреть карточку-шапку.</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Показана карточка с меткой «TRANSPORT KOMPANIYASI», ФИО пользователя (напр. «Begimbaev Naurizbek …»), названием компании (напр. «Naurizbek Trucks») и аватаром-инициалами (BN).</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход как транспортная компания.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Перейти на нижнюю вкладку «Profil».
+2. Осмотреть карточку-шапку профиля.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Показана карточка с меткой «TRANSPORT KOMPANIYASI», ФИО пользователя (напр. «Begimbaev Naurizbek …»), названием компании (напр. «Naurizbek Trucks») и аватаром с инициалами (BN).</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-053</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Плитки статистики mavjud/kutilmoqda/jarayonda</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Открыт профиль. Плитки подтверждены вживую (472 mavjud, 187 kutilmoqda, 1 jarayonda).</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть три плитки статистики под шапкой.</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Показаны три плитки: «… mavjud» (доступно), «… kutilmoqda» (ожидается), «… jarayonda» (в процессе). Значения соответствуют серверной сводке feed/summary (marketplace/won). Числа согласуются со счётчиками вкладки Takliflar.</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Открыт профиль. На тестовом аккаунте наблюдались значения: 472 mavjud, 187 kutilmoqda, 1 jarayonda.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть три плитки статистики под шапкой профиля.
+2. Сверить значения с лентой «Mavjud yuklar» и вкладкой «Takliflar».</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Показаны три плитки: «… mavjud» (доступно), «… kutilmoqda» (ожидается), «… jarayonda» (в процессе). Числа соответствуют фактическому состоянию аккаунта: согласуются со счётчиками вкладки «Takliflar» и количеством доступных грузов в ленте.</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-054</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Пункт «Bildirishnomalar» с бейджем непрочитанных</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Открыт профиль. Пункт подтверждён вживую (красный бейдж «2»).</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть пункт «Bildirishnomalar».
-2. Тапнуть по нему.</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Пункт уведомлений открывает список; тап делает уведомление прочитанным (из списка не пропадает — норм), бейдж уменьшается. Проверено 2026-07-20: функционально работает. Минус: содержимое уведомлений на китайском, не локализовано (→ BUG-032).</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Открыт профиль; у аккаунта есть непрочитанные уведомления (на пункте «Bildirishnomalar» наблюдался красный бейдж «2»).</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть пункт «Bildirishnomalar» и бейдж на нём.
+2. Нажать на пункт.
+3. Нажать на непрочитанное уведомление в списке.
+4. Вернуться и проверить бейдж.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Открывается список уведомлений. Нажатое уведомление становится прочитанным (из списка не пропадает — это норма), бейдж непрочитанных уменьшается. Проверено 2026-07-20: функционально работает. Минус: содержимое уведомлений на китайском, не локализовано (→ BUG-032).</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-056</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Переход в «Avtopark» из профиля</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Открыт профиль. Пункт «Avtopark» подтверждён вживую (значение «7 haydovchi»).</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>1. Тапнуть пункт «Avtopark» (показывает число водителей).</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Открывается экран «Avtopark» со списком водителей компании. Число водителей в пункте профиля согласуется со списком.</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Открыт профиль. В пункте «Avtopark» показано число водителей (наблюдалось «7 haydovchi»).</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать на пункт «Avtopark».</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Открывается экран «Avtopark» со списком водителей компании. Число из пункта профиля совпадает с фактическим количеством водителей в списке.</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-057</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Выход из аккаунта «Chiqish»</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Открыт профиль. Кнопка «Chiqish» (красная) подтверждена вживую.</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход, открыт профиль; внизу есть красная кнопка «Chiqish».</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Нажать «Chiqish».
-2. Подтвердить выход (если есть диалог).</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>«Chiqish» выполняет выход — возврат на экран входа, повторный вход возможен. Проверено 2026-07-20: выход работает. Замечание: нет диалога подтверждения выхода (→ BUG-033).</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
+2. Если появится диалог подтверждения — подтвердить выход.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Выполняется выход из аккаунта: происходит возврат на экран входа, повторный вход возможен. Проверено 2026-07-20: выход работает. Замечание: нет диалога подтверждения выхода (→ BUG-033).</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>mobile|session</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-058</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Профиль (Profil)</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Версия приложения в подвале</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Открыт профиль. Подвал подтверждён вживую.</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>1. Прокрутить профиль вниз до подвала.</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>Показана строка версии «Manzil-TC v1.0 · Build 2026.05».</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Открыт профиль.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Прокрутить экран профиля вниз до подвала.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>В подвале показана строка версии «Manzil-TC v1.0 · Build 2026.05».</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-059</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Happy path: список водителей компании</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Открыт «Avtopark». Экран подтверждён вживую.</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>1. Осмотреть шапку «Avtopark» со стрелкой назад.
-2. Осмотреть строку поиска и список карточек водителей.</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>Показан список карточек: аватар-инициалы, имя, код «NAMA-xxxxx», телефон, справа красная иконка-корзина. Внизу кнопка «+ Haydovchi qo'shish». Список — только водители своей компании (sort по дате создания desc).</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Открыт экран «Avtopark», у компании есть водители.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Осмотреть шапку экрана.
+2. Осмотреть строку поиска и список карточек водителей.
+3. Прокрутить список вниз до кнопки.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>В шапке — заголовок «Avtopark» и стрелка назад. В карточках водителей: аватар с инициалами, имя, код вида «NAMA-xxxxx», телефон, справа красная иконка-корзина. Внизу — кнопка «+ Haydovchi qo'shish». В списке только водители своей компании, новые сверху.</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-060</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Поиск водителя по ФИО / номеру / телефону</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>В автопарке несколько водителей. Поле «F.I.O., raqam, tel bo'yicha qidirish...» подтверждено вживую.</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести часть ФИО водителя.
-2. Очистить, ввести часть телефона.
-3. Ввести несуществующую строку.</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Список фильтруется по совпадению имени/телефона. По несуществующей строке — пустой результат. Очистка поиска возвращает полный список.</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Открыт «Avtopark», в списке несколько водителей. Вверху строка поиска «F.I.O., raqam, tel bo'yicha qidirish...».</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести в поиск часть ФИО водителя.
+2. Очистить поиск и ввести часть номера телефона.
+3. Ввести заведомо несуществующую строку.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Список фильтруется по совпадению имени/телефона. По несуществующей строке — пустой результат. После очистки поиска возвращается полный список.</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-063</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Удаление водителя из списка (красная корзина)</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>Открыт «Avtopark», водитель свободен (не на активном заказе). Красная корзина прямо в карточке — риск случайного удаления. Проверить на устройстве.</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Открыт «Avtopark»; выбранный водитель свободен (не назначен на активную заявку). Красная корзина расположена прямо на карточке, поэтому важна защита от случайного нажатия.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Нажать красную корзину на карточке свободного водителя.
-2. Проверить, появляется ли диалог подтверждения.
+2. Убедиться, что появился диалог подтверждения удаления.
 3. Подтвердить удаление.</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Показывается диалог подтверждения перед удалением (защита от случайного тапа). При подтверждении свободный водитель удаляется (сервер 204, soft-delete), карточка исчезает из списка, число в профиле уменьшается.</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Перед удалением показывается диалог подтверждения (защита от случайного нажатия). После подтверждения водитель удаляется: карточка исчезает из списка, число водителей в пункте «Avtopark» профиля уменьшается.</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-064</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Удаление занятого водителя → busy-cannot-delete</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Водитель прикреплён к активному заказу (SELECTED/IN_WORK/IN_TRANSIT).</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>В автопарке есть водитель, назначенный на активную заявку (выигранную, в работе или в пути).</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Нажать красную корзину на карточке занятого водителя.
-2. Подтвердить удаление (если есть диалог).</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Удаление занятого водителя (на активном заказе) отклоняется (busy-cannot-delete), водитель остаётся в списке. Проверено 2026-07-20: занятого водителя удалить нельзя.</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
+2. Подтвердить удаление (если появится диалог).</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Удаление не проходит: показывается сообщение об ошибке, водитель остаётся в списке. Проверено 2026-07-20: занятого водителя удалить нельзя.</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>mobile|lifecycle</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-065</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Отмена удаления в диалоге подтверждения</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Открыт «Avtopark», нажата корзина у водителя, показан диалог. Проверить на устройстве.</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>1. Нажать корзину у водителя.
-2. В диалоге подтверждения нажать «Отмена/Bekor qilish».</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Диалог подтверждения удаления появляется; после «Отмена» водитель не удаляется. Проверено 2026-07-20: отмена работает. Замечание: диалог удаления на узбекском при русском UI (→ BUG-034).</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Открыт «Avtopark», в списке есть водитель.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать корзину на карточке водителя.
+2. В появившемся диалоге подтверждения нажать «Отмена» («Bekor qilish»).</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Диалог подтверждения удаления появляется; после отмены он закрывается, водитель остаётся в списке. Проверено 2026-07-20: отмена работает. Замечание: диалог удаления на узбекском при русском UI (→ BUG-034).</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-066</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Кнопка «+ Haydovchi qo'shish» открывает форму добавления</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Открыт «Avtopark». Кнопка подтверждена вживую.</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>1. Нажать «+ Haydovchi qo'shish» внизу экрана.</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Открывается форма «Yangi haydovchi» с полями «To'liq ism», «Telefon raqam», «ID karta raqami» и кнопками «Bekor qilish»/«Saqlash».</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Открыт «Avtopark».</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать кнопку «+ Haydovchi qo'shish» внизу экрана.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Открывается форма «Yangi haydovchi» с полями «To'liq ism», «Telefon raqam», «ID karta raqami» и кнопками «Bekor qilish» и «Saqlash».</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-067</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Автопарк «Avtopark»</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Пустой автопарк (у компании нет водителей)</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Учётка без водителей.</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен вход под компанией, у которой нет ни одного водителя.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Открыть «Avtopark».</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>Пустой автопарк показывает пустое состояние («Водителей нет / Добавьте первого водителя») с иллюстрацией; приложение не падает. Проверено 2026-07-20: пустое состояние показано, локализовано (русский).</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Показывается пустое состояние с иллюстрацией и текстом вида «Водителей нет / Добавьте первого водителя». Приложение не падает. Проверено 2026-07-20: пустое состояние показано, локализовано (русский).</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>mobile|state</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-068</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Happy path: создание водителя (имя + телефон + ID-карта)</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма «Yangi haydovchi». Форма подтверждена вживую (создание до конца не прокликано — проверить на устройстве).</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi».</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. В поле «To'liq ism» ввести полное имя.
-2. В поле «Telefon raqam» ввести номер (+998, 9 цифр).
+2. В поле «Telefon raqam» ввести номер (+998 и 9 цифр).
 3. В поле «ID karta raqami» ввести номер ID-карты.
 4. Нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>Создание водителя (ФИО + телефон + ID-карта) сохраняется без ошибки, водитель появляется в списке автопарка. Проверено 2026-07-20: создание работает.</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Водитель сохраняется без ошибок и появляется в списке автопарка. Проверено 2026-07-20: создание работает.</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-069</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Валидация: пустое имя «To'liq ism» → required</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма. Сервер: @NotBlank + @Size(min=2) на fullName.</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>1. Оставить «To'liq ism» пустым.
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi».</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Оставить поле «To'liq ism» пустым.
 2. Заполнить телефон.
 3. Нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>Сохранение блокируется: обязательное поле имени. Показывается ошибка «обязательно» (сервер 400, field=fullName). Водитель не создаётся.</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение не проходит: показывается сообщение, что имя обязательно. Водитель не создаётся.</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-070</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Валидация: имя из 1 символа → too-short (границы 2..255)</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма. Сервер: @Size(min=2,max=255) на fullName.</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести имя из 1 символа.
-2. Заполнить телефон и сохранить.
-3. Повторить с именем из 2 символов.</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>1 символ — отклоняется (400, @Size min=2). 2 символа — принимается. Приложение показывает ошибку длины на слишком коротком имени.</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi». Допустимая длина имени — от 2 до 255 символов.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести имя из 1 символа и корректный телефон.
+2. Нажать «Saqlash».
+3. Исправить имя на 2 символа и снова нажать «Saqlash».</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>С именем из 1 символа сохранение не проходит — показывается сообщение о слишком коротком имени, водитель не создаётся. С именем из 2 символов водитель сохраняется.</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-071</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Валидация: пустой телефон → required</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма. Сервер: @NotBlank на phone.</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi».</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Заполнить имя.
-2. Оставить «Telefon raqam» пустым.
+2. Оставить поле «Telefon raqam» пустым.
 3. Нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>Сохранение блокируется: телефон обязателен (сервер 400, field=phone). Водитель не создаётся.</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение не проходит: показывается сообщение, что телефон обязателен. Водитель не создаётся.</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-072</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Валидация формата телефона (E.164 +[10..15] цифр)</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма. Поле телефона с префиксом +998. Сервер: @Pattern ^\+[0-9]{10,15}$.</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести слишком короткий номер (меньше 9 нац. цифр).
-2. Попытаться ввести буквы/символы.
-3. Сохранить.</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>Слишком короткий/невалидный номер отклоняется (клиентская маска и/или сервер 400 @Pattern, field=phone). Буквы не вводятся. Валидный узбекский номер (+998 + 9 цифр = 12 знаков) проходит.</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi», поле телефона с префиксом +998. Номер проверяется по международному формату: «+» и от 10 до 15 цифр.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Ввести слишком короткий номер (меньше 9 цифр после +998).
+2. Попробовать ввести буквы и символы.
+3. Нажать «Saqlash».</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Слишком короткий или невалидный номер не сохраняется: маска не даёт его ввести либо показывается сообщение об ошибке формата телефона. Буквы не вводятся. Полный узбекский номер (+998 и ещё 9 цифр — всего 12 цифр) принимается.</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-073</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Дубликат телефона в компании → phone-exists</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>В компании уже есть водитель с таким телефоном. Сервер: existsByTransportCompanyIdAndPhone.</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi». В этой же компании уже есть водитель с известным номером телефона.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Ввести имя и телефон, уже занятый другим водителем компании.
 2. Нажать «Saqlash».</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>Создание отклоняется: сервер 409, code=error.driver.phone-exists. Приложение показывает, что водитель с таким номером уже существует; дубликат не создаётся.</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Создание отклоняется: показывается сообщение, что водитель с таким номером уже существует. Дубликат не создаётся.</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>mobile|negative</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-074</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>ID-карта необязательна при создании; нужна при назначении</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма. Сервер: cardId опционален при создании (@Size max=32), но требуется при прикреплении к заказу.</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>1. Заполнить имя и телефон, поле «ID karta raqami» оставить пустым.
-2. Сохранить.
-3. Позже попытаться назначить этого водителя на выигранный груз без cardId.</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>ID-карта необязательна при создании водителя (сохраняется без неё), но требуется при назначении на груз (просят ввести / card-id-required). Проверено 2026-07-20: без ID-карты сохраняется; при назначении ID-карту требуют. Примечание: форма добавления на узбекском при русском UI (→ BUG-034).</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi». У компании есть выигранный груз, чтобы затем проверить назначение.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Заполнить имя и телефон; поле «ID karta raqami» оставить пустым.
+2. Нажать «Saqlash».
+3. Позже попытаться назначить этого водителя на выигранный груз.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Водитель без ID-карты создаётся успешно. При назначении на груз приложение требует указать ID-карту — без неё назначение не проходит. Проверено 2026-07-20: без ID-карты сохраняется; при назначении ID-карту требуют. Примечание: форма добавления на узбекском при русском UI (→ BUG-034).</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-075</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Граница длины ID-карты (max 32 символа)</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма. Сервер: @Size(max=32) на cardId.</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести ID-карту длиной 32 символа и сохранить.
-2. Ввести ID-карту длиной 33 символа и сохранить.</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>32 символа — принимается (201). 33 символа — отклоняется (400, @Size max=32, too-long). Приложение ограничивает длину/показывает ошибку.</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi»; имя и телефон заполнены корректно. Максимальная длина ID-карты — 32 символа.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. В поле «ID karta raqami» ввести значение ровно из 32 символов.
+2. Нажать «Saqlash».
+3. Начать создание второго водителя (с другим телефоном) и ввести ID-карту из 33 символов.
+4. Нажать «Saqlash».</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Значение из 32 символов принимается — водитель сохраняется. Значение из 33 символов не сохраняется: поле не даёт ввести лишний символ либо показывается ошибка о превышении допустимой длины.</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>mobile|validation</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-076</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Кнопка «Bekor qilish» отменяет создание</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма, частично заполнена.</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>1. Заполнить часть полей.
-2. Нажать «Bekor qilish».</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>Форма закрывается без создания водителя; возврат в «Avtopark», список без изменений.</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi», часть полей заполнена.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Нажать «Bekor qilish».</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Форма закрывается, водитель не создаётся; происходит возврат на экран «Avtopark», список без изменений.</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>mobile|positive</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-077</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Форма добавления водителя «Yangi haydovchi»</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Защита от двойного тапа по «Saqlash»</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма, поля валидны.</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>1. Заполнить валидные данные.
-2. Быстро дважды нажать «Saqlash».</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>Двойной быстрый тап по «Saqlash» создаёт только одного водителя (без дубля); кнопка блокируется после первого тапа. Проверено 2026-07-20: кнопка становится неактивной после первого нажатия, дубля нет.</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Yangi haydovchi», все поля заполнены корректно.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Быстро нажать «Saqlash» два раза подряд.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Создаётся только один водитель, дубликата в списке нет. Проверено 2026-07-20: кнопка становится неактивной после первого нажатия, дубля нет.</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>mobile|network</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-079</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Двойной тап по «Yuborish» при подаче оффера</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Открыта форма оффера, введена цена.</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>1. Ввести цену.
-2. Быстро дважды нажать «Yuborish».</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>Двойной быстрый тап по «Yuborish» создаёт только одно предложение (без дубля); кнопка блокируется после первого тапа. Проверено 2026-07-20: дубля нет, кнопка блокируется.</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Открыта форма «Taklif yuborish», введена цена.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Быстро нажать «Yuborish» два раза подряд.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Создаётся только одно предложение, дубликата нет. Проверено 2026-07-20: дубля нет, кнопка блокируется.</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>mobile|network</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-080</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Сворачивание в фон и возврат сохраняют состояние</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>Открыт любой экран (например форма оффера с введённой ценой).</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>1. Свернуть приложение (Home), открыть другое приложение.
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Открыт любой экран с введёнными данными — например форма «Taklif yuborish» с заполненной ценой.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Свернуть приложение кнопкой Home и открыть любое другое приложение.
 2. Вернуться в приложение перевозчика.</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>Сворачивание в фон и возврат сохраняют состояние: приложение возвращается на тот же экран, введённое не потеряно, не выкидывает на старт/логин. Проверено 2026-07-20: возвращается на то же место.</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Приложение открывается на том же экране, введённые данные не потеряны; на стартовый экран или экран входа не выбрасывает. Проверено 2026-07-20: возвращается на то же место.</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>mobile|session</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>MOB-CR-084</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Мобайл — Приложение перевозчика</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Мобайл — Приложение перевозчика</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Кросс-функциональное</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Навигация назад системной кнопкой Android</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>Открыт вложенный экран (детали груза / форма оффера / добавление водителя).</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>1. Открыть форму оффера с введённой ценой.
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Открыт вложенный экран: детали груза, форма предложения или форма добавления водителя.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть форму предложения и ввести цену.
 2. Нажать системную кнопку «Назад» Android.</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>Системная кнопка «Назад» Android возвращает на предыдущий экран пошагово (не закрывает приложение сразу, не выкидывает на логин); с главного экрана — обычное поведение. Проверено 2026-07-20: навигация назад работает.</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Возврат выполняется на предыдущий экран пошагово: приложение не закрывается сразу и не выбрасывает на экран входа. С главного экрана кнопка «Назад» работает как обычно. Проверено 2026-07-20: навигация назад работает.</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>mobile|session</t>
         </is>
